--- a/事務所資料/事務所基本情報/経営＆事業数字.xlsx
+++ b/事務所資料/事務所基本情報/経営＆事業数字.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\claudeマスター\事務所基本情報\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\claudeマスター\事務所資料\事務所基本情報\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F388FDC-A768-46F7-9CB0-894DC9C4A442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671BED92-0DCB-4F63-9F8F-943CE90DF538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{0AC15293-5510-41CE-A57E-9A87D7AC23FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="改宗" sheetId="3" r:id="rId3"/>
+    <sheet name="回収サマリー" sheetId="3" r:id="rId3"/>
+    <sheet name="回収（２６年２月実数値）" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="263">
   <si>
     <t>夏から２００返す想定。→３月城南相談</t>
     <rPh sb="0" eb="1">
@@ -1714,6 +1715,577 @@
     <t>粗利</t>
     <rPh sb="0" eb="2">
       <t>アラリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>収支（2月）</t>
+    <rPh sb="0" eb="2">
+      <t>シュウシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガツ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>収入</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>項目</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>金額</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>エラン（A）</t>
+  </si>
+  <si>
+    <t>エランその他</t>
+    <rPh sb="5" eb="6">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>川島</t>
+    <rPh sb="0" eb="2">
+      <t>カワシマ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エラン（B）</t>
+  </si>
+  <si>
+    <t>sms</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>2/18￥953012入金あり　ベンヒ23％</t>
+    <rPh sb="11" eb="13">
+      <t>ニュウキン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>山本</t>
+    <rPh sb="0" eb="2">
+      <t>ヤマモト</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エラン（C）</t>
+  </si>
+  <si>
+    <t>合計（税抜き）</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼイヌ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>香美</t>
+    <rPh sb="0" eb="2">
+      <t>カガミ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>エランサービス</t>
+  </si>
+  <si>
+    <t>帯島</t>
+    <rPh sb="0" eb="2">
+      <t>オビシマ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>小山</t>
+    <rPh sb="0" eb="2">
+      <t>コヤマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>堀</t>
+    <rPh sb="0" eb="1">
+      <t>ホリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あもうA</t>
+  </si>
+  <si>
+    <t>支出</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>笠原</t>
+    <rPh sb="0" eb="2">
+      <t>カサハラ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>あもうB</t>
+  </si>
+  <si>
+    <t>佐口</t>
+    <rPh sb="0" eb="2">
+      <t>サグチ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブランディング</t>
+  </si>
+  <si>
+    <t>人件費</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>回収メンバー歩合15万込み</t>
+    <rPh sb="0" eb="2">
+      <t>カイシュウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブアイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>布野</t>
+    <rPh sb="0" eb="2">
+      <t>フノ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ベネフィット</t>
+  </si>
+  <si>
+    <t>アタラヨ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>88万（7割負担）</t>
+    <rPh sb="2" eb="3">
+      <t>マン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>フタン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>社保込み</t>
+    <rPh sb="0" eb="3">
+      <t>シャホコ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マイズ</t>
+  </si>
+  <si>
+    <t>189310（5割負担）</t>
+    <rPh sb="8" eb="9">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>フタン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>瀧ノ上</t>
+    <rPh sb="0" eb="1">
+      <t>タキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ウエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マイナビ（バイト）</t>
+  </si>
+  <si>
+    <t>コピー機</t>
+    <rPh sb="3" eb="4">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>使用料15840</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>大岩</t>
+    <rPh sb="0" eb="2">
+      <t>オオイワ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マイナビ（転職）</t>
+    <rPh sb="5" eb="7">
+      <t>テンショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラン支払督促実費</t>
+    <rPh sb="3" eb="7">
+      <t>シハライトクソク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ジッピ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>南九</t>
+    <rPh sb="0" eb="2">
+      <t>ナンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホムコム</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>使用料16500</t>
+    <rPh sb="0" eb="3">
+      <t>シヨウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ハウスリーブ</t>
+  </si>
+  <si>
+    <t>郵送代</t>
+    <rPh sb="0" eb="3">
+      <t>ユウソウダイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GMO</t>
+  </si>
+  <si>
+    <t>自動織機レンタル代</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショッキ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レンティオA</t>
+  </si>
+  <si>
+    <t>ｓｍｓ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブラストメール込み（16500）</t>
+    <rPh sb="7" eb="8">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レンティオA（返却）</t>
+    <rPh sb="7" eb="9">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｓｍｓ(双方向)</t>
+    <rPh sb="4" eb="7">
+      <t>ソウホウコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>7末解約（契約期間の縛りがあったため）</t>
+    <rPh sb="1" eb="2">
+      <t>マツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイヤク</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>ケイヤクキカン</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>シバ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レンティオB</t>
+  </si>
+  <si>
+    <t>ブルービーン</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>レンティオB（返却）</t>
+    <rPh sb="7" eb="9">
+      <t>ヘンキャク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チャットプラス㈱</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>3月解約</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カイヤク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>シンフォニカル</t>
+  </si>
+  <si>
+    <t>電話代</t>
+    <rPh sb="0" eb="2">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>312,539（8割負担）</t>
+    <rPh sb="9" eb="10">
+      <t>ワリ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>フタン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>カーサ</t>
+  </si>
+  <si>
+    <t>島田さん</t>
+    <rPh sb="0" eb="2">
+      <t>シマダ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>手数料￥１３０</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>振込手数料</t>
+    <rPh sb="0" eb="2">
+      <t>フリコミ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>テスウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>仮</t>
+    <rPh sb="0" eb="1">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>東上セレモ</t>
+    <rPh sb="0" eb="2">
+      <t>トウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雑費</t>
+    <rPh sb="0" eb="2">
+      <t>ザッピ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クラス</t>
+  </si>
+  <si>
+    <t>合計</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>ラクーン</t>
+  </si>
+  <si>
+    <t>ライフスタイルウォーター</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>収入金額合計(税込み)</t>
+    <rPh sb="0" eb="2">
+      <t>シュウニュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゼイコ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>支出金額合計</t>
+    <rPh sb="0" eb="2">
+      <t>シシュツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>差し引き金額</t>
+    <rPh sb="0" eb="1">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キンガク</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>人件費率</t>
+    <rPh sb="0" eb="4">
+      <t>ジンケンヒリツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>経費率</t>
+    <rPh sb="0" eb="3">
+      <t>ケイヒリツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>主要クライアント</t>
+    <rPh sb="0" eb="2">
+      <t>シュヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>プレミアムウォーター株式会社</t>
+    <rPh sb="10" eb="14">
+      <t>カブシキカイシャ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>株式会社sms</t>
+    <rPh sb="0" eb="4">
+      <t>カブシキカイシャ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>小山株式会社</t>
+    <rPh sb="0" eb="2">
+      <t>コヤマ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カブシキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイシャ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GMOペイメントサービス株式会社</t>
+    <rPh sb="12" eb="16">
+      <t>カブシキガイシャ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1722,11 +2294,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
+    <numFmt numFmtId="5" formatCode="&quot;¥&quot;#,##0;&quot;¥&quot;\-#,##0"/>
+    <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="177" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1812,8 +2387,67 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1898,8 +2532,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1996,8 +2648,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2007,8 +2754,11 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2038,15 +2788,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2171,11 +2912,120 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="3" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="3" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="15" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="パーセント" xfId="2" builtinId="5"/>
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="3" xr:uid="{9DAA2E15-D2B9-41E6-BEFE-B8DA8BEB58B4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2508,19 +3358,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BDAA18-F9BD-43BC-A602-6E052DBFAD9A}">
   <dimension ref="A1:Q140"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="38.6640625" customWidth="1"/>
     <col min="2" max="2" width="10.9140625" customWidth="1"/>
     <col min="3" max="8" width="11.4140625" customWidth="1"/>
-    <col min="9" max="9" width="11.4140625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="11.4140625" style="10" customWidth="1"/>
     <col min="10" max="11" width="11.4140625" customWidth="1"/>
-    <col min="12" max="12" width="11.4140625" style="13" customWidth="1"/>
+    <col min="12" max="12" width="11.4140625" style="10" customWidth="1"/>
     <col min="13" max="16" width="11.4140625" customWidth="1"/>
     <col min="17" max="17" width="13.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2573,7 +3423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:17" s="5" customFormat="1" ht="18.5" thickBot="1">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -2591,20 +3441,20 @@
       <c r="L2" s="7"/>
       <c r="Q2" s="8"/>
     </row>
-    <row r="3" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:17" ht="18.5" thickBot="1">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="53"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2637,12 +3487,12 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="14">
+      <c r="Q4" s="11">
         <f>SUM(E4:P4)</f>
         <v>3000000</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2680,24 +3530,24 @@
       <c r="L5" s="7">
         <v>22000000</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="12">
         <v>22000000</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="12">
         <v>22000000</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="12">
         <v>22000000</v>
       </c>
-      <c r="P5" s="15">
+      <c r="P5" s="12">
         <v>22000000</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="11">
         <f>SUM(E5:P5)</f>
         <v>215000000</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2716,9 +3566,9 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="14"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q6" s="11"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2767,12 +3617,12 @@
       <c r="P7" s="5">
         <v>18000000</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="11">
         <f t="shared" ref="Q7:Q24" si="0">SUM(E7:P7)</f>
         <v>175500000</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2794,9 +3644,9 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="14"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q8" s="11"/>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2845,12 +3695,12 @@
       <c r="P9" s="5">
         <v>9000000</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="11">
         <f t="shared" si="0"/>
         <v>117000000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2869,9 +3719,9 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
-      <c r="Q10" s="14"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q10" s="11"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2893,12 +3743,12 @@
       <c r="N11" s="7"/>
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
-      <c r="Q11" s="14">
+      <c r="Q11" s="11">
         <f>SUM(F11:P11)</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2918,9 +3768,9 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
-      <c r="Q12" s="14"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q12" s="11"/>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2954,21 +3804,21 @@
       <c r="M13" s="5">
         <v>2000000</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="12">
         <v>2500000</v>
       </c>
-      <c r="O13" s="15">
+      <c r="O13" s="12">
         <v>2500000</v>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="12">
         <v>2500000</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="Q13" s="11">
         <f t="shared" si="0"/>
         <v>23000000</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2986,9 +3836,9 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
-      <c r="Q14" s="14"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q14" s="11"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -3021,12 +3871,12 @@
       <c r="P15" s="5">
         <v>1500000</v>
       </c>
-      <c r="Q15" s="14">
+      <c r="Q15" s="11">
         <f t="shared" si="0"/>
         <v>8000000</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -3071,12 +3921,12 @@
       <c r="P16" s="5">
         <v>800000</v>
       </c>
-      <c r="Q16" s="14">
+      <c r="Q16" s="11">
         <f t="shared" si="0"/>
         <v>9600000</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -3095,9 +3945,9 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
       <c r="P17" s="5"/>
-      <c r="Q17" s="14"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q17" s="11"/>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -3115,12 +3965,12 @@
       <c r="M18" s="5"/>
       <c r="O18" s="5"/>
       <c r="P18" s="5"/>
-      <c r="Q18" s="14">
+      <c r="Q18" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -3138,9 +3988,9 @@
       <c r="M19" s="5"/>
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
-      <c r="Q19" s="14"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q19" s="11"/>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -3157,12 +4007,12 @@
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
-      <c r="Q20" s="14">
+      <c r="Q20" s="11">
         <f>SUM(E20:P20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -3180,9 +4030,9 @@
       <c r="M21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
-      <c r="Q21" s="14"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -3200,78 +4050,78 @@
       <c r="M22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
-      <c r="Q22" s="14"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="16" t="s">
+      <c r="Q22" s="11"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="14">
         <f>SUM(B4:B22)</f>
         <v>41331144</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <f t="shared" ref="C23:Q23" si="1">SUM(C4:C22)</f>
         <v>38700000</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="14">
         <f t="shared" si="1"/>
         <v>33400000</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="14">
         <f t="shared" si="1"/>
         <v>32400000</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="14">
         <f t="shared" si="1"/>
         <v>36500000</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="14">
         <f t="shared" si="1"/>
         <v>45900000</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="14">
         <f t="shared" si="1"/>
         <v>39300000</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="15">
         <f>SUM(I3:I21)</f>
         <v>44500000</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="14">
         <f t="shared" si="1"/>
         <v>44500000</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="14">
         <f t="shared" si="1"/>
         <v>47500000</v>
       </c>
-      <c r="L23" s="18">
+      <c r="L23" s="15">
         <f t="shared" si="1"/>
         <v>49600000</v>
       </c>
-      <c r="M23" s="17">
+      <c r="M23" s="14">
         <f t="shared" si="1"/>
         <v>52800000</v>
       </c>
-      <c r="N23" s="17">
+      <c r="N23" s="14">
         <f t="shared" si="1"/>
         <v>53800000</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="14">
         <f t="shared" si="1"/>
         <v>54800000</v>
       </c>
-      <c r="P23" s="17">
+      <c r="P23" s="14">
         <f t="shared" si="1"/>
         <v>53800000</v>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="16">
         <f t="shared" si="1"/>
         <v>551400000</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -3320,12 +4170,12 @@
       <c r="P24" s="5">
         <v>1000000</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="Q24" s="11">
         <f t="shared" si="0"/>
         <v>17250000</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -3376,77 +4226,77 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="16" t="s">
+    <row r="26" spans="1:17">
+      <c r="A26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="14">
         <f>SUM(B23:B25)</f>
         <v>46112891</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="14">
         <f>SUM(C23:C25)</f>
         <v>42200000</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="14">
         <f t="shared" ref="D26:P26" si="2">SUM(D23:D25)</f>
         <v>36335000</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="14">
         <f>SUM(E23:E25)</f>
         <v>35400000</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="14">
         <f t="shared" si="2"/>
         <v>39800000</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="14">
         <f t="shared" si="2"/>
         <v>47900000</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="14">
         <f t="shared" si="2"/>
         <v>41300000</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="15">
         <f t="shared" si="2"/>
         <v>46300000</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="14">
         <f t="shared" si="2"/>
         <v>46300000</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="14">
         <f t="shared" si="2"/>
         <v>49050000</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="15">
         <f t="shared" si="2"/>
         <v>51150000</v>
       </c>
-      <c r="M26" s="17">
+      <c r="M26" s="14">
         <f t="shared" si="2"/>
         <v>54350000</v>
       </c>
-      <c r="N26" s="17">
+      <c r="N26" s="14">
         <f t="shared" si="2"/>
         <v>55100000</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="14">
         <f t="shared" si="2"/>
         <v>56100000</v>
       </c>
-      <c r="P26" s="17">
+      <c r="P26" s="14">
         <f t="shared" si="2"/>
         <v>55100000</v>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="16">
         <f>SUM(Q23:Q25)</f>
         <v>568650000</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="20" t="s">
+    <row r="27" spans="1:17">
+      <c r="A27" s="17" t="s">
         <v>31</v>
       </c>
       <c r="B27" s="5"/>
@@ -3465,7 +4315,7 @@
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -3485,7 +4335,7 @@
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -3513,7 +4363,7 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -3541,7 +4391,7 @@
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -3569,7 +4419,7 @@
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -3595,7 +4445,7 @@
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -3624,7 +4474,7 @@
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -3652,7 +4502,7 @@
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -3676,7 +4526,7 @@
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -3698,7 +4548,7 @@
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -3718,19 +4568,19 @@
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="21" t="s">
+    <row r="38" spans="1:16">
+      <c r="A38" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B38" s="22">
+      <c r="B38" s="19">
         <f>SUM(B29:B37)</f>
         <v>19074559</v>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="19">
         <f>SUM(C29:C37)</f>
         <v>19004931</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="19">
         <v>18500000</v>
       </c>
       <c r="E38" s="5">
@@ -3751,11 +4601,11 @@
         <f t="shared" si="3"/>
         <v>20800000</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="12">
         <f>J5*0.25+J7*0.6+J9*0.3+J11*0.35+J13*0.3+J15*0.3+J20*0.5+1800000+1000000+500000</f>
         <v>20000000</v>
       </c>
-      <c r="K38" s="15">
+      <c r="K38" s="12">
         <f t="shared" ref="K38:P38" si="4">K5*0.25+K7*0.6+K9*0.3+K11*0.35+K13*0.3+K15*0.3+K20*0.5+1800000+1000000+500000</f>
         <v>20850000</v>
       </c>
@@ -3763,93 +4613,93 @@
         <f t="shared" si="4"/>
         <v>21400000</v>
       </c>
-      <c r="M38" s="15">
+      <c r="M38" s="12">
         <f t="shared" si="4"/>
         <v>22750000</v>
       </c>
-      <c r="N38" s="15">
+      <c r="N38" s="12">
         <f t="shared" si="4"/>
         <v>23500000</v>
       </c>
-      <c r="O38" s="15">
+      <c r="O38" s="12">
         <f t="shared" si="4"/>
         <v>23800000</v>
       </c>
-      <c r="P38" s="15">
+      <c r="P38" s="12">
         <f t="shared" si="4"/>
         <v>23500000</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="21" t="s">
+    <row r="39" spans="1:16">
+      <c r="A39" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B39" s="20">
         <f>B38/B26</f>
         <v>0.41364916808187108</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="20">
         <f>C38/C26</f>
         <v>0.4503538151658768</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="20">
         <f t="shared" ref="D39:P39" si="5">D38/D26</f>
         <v>0.50915095637814778</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="20">
         <f t="shared" si="5"/>
         <v>0.56497175141242939</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="20">
         <f t="shared" si="5"/>
         <v>0.49447707788944723</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="20">
         <f t="shared" si="5"/>
         <v>0.40334029227557411</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="20">
         <f t="shared" si="5"/>
         <v>0.46004842615012109</v>
       </c>
-      <c r="I39" s="24">
+      <c r="I39" s="21">
         <f t="shared" si="5"/>
         <v>0.44924406047516197</v>
       </c>
-      <c r="J39" s="23">
+      <c r="J39" s="20">
         <f t="shared" si="5"/>
         <v>0.43196544276457882</v>
       </c>
-      <c r="K39" s="23">
+      <c r="K39" s="20">
         <f t="shared" si="5"/>
         <v>0.42507645259938837</v>
       </c>
-      <c r="L39" s="24">
+      <c r="L39" s="21">
         <f t="shared" si="5"/>
         <v>0.41837732160312807</v>
       </c>
-      <c r="M39" s="23">
+      <c r="M39" s="20">
         <f t="shared" si="5"/>
         <v>0.41858325666973323</v>
       </c>
-      <c r="N39" s="23">
+      <c r="N39" s="20">
         <f t="shared" si="5"/>
         <v>0.426497277676951</v>
       </c>
-      <c r="O39" s="23">
+      <c r="O39" s="20">
         <f t="shared" si="5"/>
         <v>0.42424242424242425</v>
       </c>
-      <c r="P39" s="23">
+      <c r="P39" s="20">
         <f t="shared" si="5"/>
         <v>0.426497277676951</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="23"/>
+      <c r="B40" s="20"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -3867,11 +4717,11 @@
       <c r="O40" s="5"/>
       <c r="P40" s="5"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>47</v>
       </c>
-      <c r="B41" s="23"/>
+      <c r="B41" s="20"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -3889,11 +4739,11 @@
       <c r="O41" s="5"/>
       <c r="P41" s="5"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="23"/>
+      <c r="B42" s="20"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -3909,11 +4759,11 @@
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="23"/>
+      <c r="B43" s="20"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -3929,11 +4779,11 @@
       <c r="O43" s="5"/>
       <c r="P43" s="5"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="23"/>
+      <c r="B44" s="20"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -3949,7 +4799,7 @@
       <c r="O44" s="5"/>
       <c r="P44" s="5"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -3969,18 +4819,18 @@
       <c r="O45" s="5"/>
       <c r="P45" s="5"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>53</v>
       </c>
       <c r="B46" s="5">
         <v>2461866</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="22">
         <v>2461866</v>
       </c>
       <c r="D46" s="5"/>
-      <c r="E46" s="25">
+      <c r="E46" s="22">
         <v>2461866</v>
       </c>
       <c r="F46" s="5"/>
@@ -3995,18 +4845,18 @@
       <c r="O46" s="5"/>
       <c r="P46" s="5"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>54</v>
       </c>
       <c r="B47" s="5">
         <v>200750</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="22">
         <v>200750</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="E47" s="25">
+      <c r="E47" s="22">
         <v>200750</v>
       </c>
       <c r="F47" s="5"/>
@@ -4021,14 +4871,14 @@
       <c r="O47" s="5"/>
       <c r="P47" s="5"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>55</v>
       </c>
       <c r="B48" s="5">
         <v>279473</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="22">
         <v>279473</v>
       </c>
       <c r="D48" s="5"/>
@@ -4045,14 +4895,14 @@
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>56</v>
       </c>
       <c r="B49" s="5">
         <v>199430</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="22">
         <v>199430</v>
       </c>
       <c r="D49" s="5"/>
@@ -4071,7 +4921,7 @@
       <c r="O49" s="5"/>
       <c r="P49" s="5"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -4079,7 +4929,7 @@
         <f>842253+220000</f>
         <v>1062253</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="22">
         <v>1000000</v>
       </c>
       <c r="D50" s="5">
@@ -4108,11 +4958,11 @@
       <c r="O50" s="5"/>
       <c r="P50" s="5"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="21" t="s">
+    <row r="51" spans="1:16">
+      <c r="A51" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="19">
         <f>SUM(B46:B50)</f>
         <v>4203772</v>
       </c>
@@ -4159,7 +5009,7 @@
         <v>3600000</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -4179,7 +5029,7 @@
       <c r="O52" s="5"/>
       <c r="P52" s="5"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -4192,7 +5042,7 @@
       <c r="D53" s="5">
         <v>5000000</v>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="22">
         <v>4500000</v>
       </c>
       <c r="F53" s="5">
@@ -4239,7 +5089,7 @@
         <v>8800000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -4269,7 +5119,7 @@
       <c r="O54" s="5"/>
       <c r="P54" s="5"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -4317,7 +5167,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -4377,7 +5227,7 @@
         <v>2380000</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -4407,7 +5257,7 @@
       <c r="O57" s="5"/>
       <c r="P57" s="5"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -4429,72 +5279,72 @@
       <c r="O58" s="5"/>
       <c r="P58" s="5"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="21" t="s">
+    <row r="59" spans="1:16">
+      <c r="A59" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="19">
         <f>SUM(B53:B58)</f>
         <v>10282061</v>
       </c>
-      <c r="C59" s="26">
+      <c r="C59" s="23">
         <f>SUM(C53:C58)</f>
         <v>8822016</v>
       </c>
-      <c r="D59" s="26">
+      <c r="D59" s="23">
         <f>SUM(D53:D58)</f>
         <v>7482800</v>
       </c>
-      <c r="E59" s="26">
+      <c r="E59" s="23">
         <f t="shared" ref="E59:P59" si="8">SUM(E53:E58)</f>
         <v>7187000</v>
       </c>
-      <c r="F59" s="26">
+      <c r="F59" s="23">
         <f t="shared" si="8"/>
         <v>5472800</v>
       </c>
-      <c r="G59" s="26">
+      <c r="G59" s="23">
         <f t="shared" si="8"/>
         <v>8150000</v>
       </c>
-      <c r="H59" s="26">
+      <c r="H59" s="23">
         <f t="shared" si="8"/>
         <v>7700000</v>
       </c>
-      <c r="I59" s="27">
+      <c r="I59" s="24">
         <f t="shared" si="8"/>
         <v>7700000</v>
       </c>
-      <c r="J59" s="26">
+      <c r="J59" s="23">
         <f t="shared" si="8"/>
         <v>8780000</v>
       </c>
-      <c r="K59" s="26">
+      <c r="K59" s="23">
         <f t="shared" si="8"/>
         <v>8780000</v>
       </c>
-      <c r="L59" s="27">
+      <c r="L59" s="24">
         <f t="shared" si="8"/>
         <v>9320000</v>
       </c>
-      <c r="M59" s="26">
+      <c r="M59" s="23">
         <f t="shared" si="8"/>
         <v>11480000</v>
       </c>
-      <c r="N59" s="26">
+      <c r="N59" s="23">
         <f t="shared" si="8"/>
         <v>11480000</v>
       </c>
-      <c r="O59" s="26">
+      <c r="O59" s="23">
         <f t="shared" si="8"/>
         <v>11480000</v>
       </c>
-      <c r="P59" s="26">
+      <c r="P59" s="23">
         <f t="shared" si="8"/>
         <v>11480000</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -4514,7 +5364,7 @@
       <c r="O60" s="5"/>
       <c r="P60" s="5"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -4536,7 +5386,7 @@
       <c r="O61" s="5"/>
       <c r="P61" s="5"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -4558,7 +5408,7 @@
       <c r="O62" s="5"/>
       <c r="P62" s="5"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -4580,7 +5430,7 @@
       <c r="O63" s="5"/>
       <c r="P63" s="5"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -4602,7 +5452,7 @@
       <c r="O64" s="5"/>
       <c r="P64" s="5"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -4646,11 +5496,11 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="21" t="s">
+    <row r="66" spans="1:16">
+      <c r="A66" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B66" s="22">
+      <c r="B66" s="19">
         <f>SUM(B61:B64)</f>
         <v>3138893</v>
       </c>
@@ -4684,7 +5534,7 @@
         <f t="shared" ref="J66" si="10">J9*0.3+J11*0.6+J13*0.2+J65</f>
         <v>3900000</v>
       </c>
-      <c r="K66" s="15">
+      <c r="K66" s="12">
         <f>K9*0.3+K11*0.55+K13*0.2+K15*0.35+K65</f>
         <v>4300000</v>
       </c>
@@ -4692,24 +5542,24 @@
         <f t="shared" ref="L66:P66" si="11">L9*0.3+L11*0.55+L13*0.2+L15*0.35+L65</f>
         <v>3850000</v>
       </c>
-      <c r="M66" s="15">
+      <c r="M66" s="12">
         <f t="shared" si="11"/>
         <v>4300000</v>
       </c>
-      <c r="N66" s="15">
+      <c r="N66" s="12">
         <f t="shared" si="11"/>
         <v>4125000</v>
       </c>
-      <c r="O66" s="15">
+      <c r="O66" s="12">
         <f t="shared" si="11"/>
         <v>4425000</v>
       </c>
-      <c r="P66" s="15">
+      <c r="P66" s="12">
         <f t="shared" si="11"/>
         <v>4125000</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
         <v>73</v>
       </c>
@@ -4731,7 +5581,7 @@
       <c r="O67" s="5"/>
       <c r="P67" s="5"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>75</v>
       </c>
@@ -4778,7 +5628,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -4810,73 +5660,73 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="21" t="s">
+    <row r="70" spans="1:16">
+      <c r="A70" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="19">
         <f>SUM(B67:B69)</f>
         <v>0</v>
       </c>
-      <c r="C70" s="26">
+      <c r="C70" s="23">
         <f t="shared" ref="C70:P70" si="12">SUM(C67:C69)</f>
         <v>2000000</v>
       </c>
-      <c r="D70" s="26">
+      <c r="D70" s="23">
         <f t="shared" si="12"/>
         <v>4000000</v>
       </c>
-      <c r="E70" s="26">
+      <c r="E70" s="23">
         <f t="shared" si="12"/>
         <v>2000000</v>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="23">
         <f t="shared" si="12"/>
         <v>695090</v>
       </c>
-      <c r="G70" s="26">
+      <c r="G70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="H70" s="26">
+      <c r="H70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="I70" s="27">
+      <c r="I70" s="24">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="J70" s="26">
+      <c r="J70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="K70" s="26">
+      <c r="K70" s="23">
         <f t="shared" si="12"/>
         <v>7750000</v>
       </c>
-      <c r="L70" s="27">
+      <c r="L70" s="24">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="M70" s="26">
+      <c r="M70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="N70" s="26">
+      <c r="N70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="O70" s="26">
+      <c r="O70" s="23">
         <f t="shared" si="12"/>
         <v>750000</v>
       </c>
-      <c r="P70" s="26">
+      <c r="P70" s="23">
         <f t="shared" si="12"/>
         <v>8750000</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="28"/>
+    <row r="71" spans="1:16">
+      <c r="B71" s="25"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
@@ -4892,7 +5742,7 @@
       <c r="O71" s="5"/>
       <c r="P71" s="5"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -4912,7 +5762,7 @@
       <c r="O72" s="5"/>
       <c r="P72" s="5"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>80</v>
       </c>
@@ -4962,7 +5812,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>81</v>
       </c>
@@ -4985,11 +5835,11 @@
       <c r="O74" s="5"/>
       <c r="P74" s="5"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="21" t="s">
+    <row r="75" spans="1:16">
+      <c r="A75" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="19">
         <f>SUM(B73:B74)</f>
         <v>3412645</v>
       </c>
@@ -4997,60 +5847,60 @@
         <f>SUM(C73:C74)</f>
         <v>1430000</v>
       </c>
-      <c r="D75" s="26">
+      <c r="D75" s="23">
         <f>SUM(D73:D74)</f>
         <v>1000000</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="23">
         <f t="shared" ref="E75:P75" si="13">SUM(E73:E74)</f>
         <v>2000000</v>
       </c>
-      <c r="F75" s="26">
+      <c r="F75" s="23">
         <f t="shared" si="13"/>
         <v>3900000</v>
       </c>
-      <c r="G75" s="26">
+      <c r="G75" s="23">
         <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
-      <c r="H75" s="26">
+      <c r="H75" s="23">
         <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
-      <c r="I75" s="27">
+      <c r="I75" s="24">
         <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
-      <c r="J75" s="26">
+      <c r="J75" s="23">
         <f t="shared" si="13"/>
         <v>2000000</v>
       </c>
-      <c r="K75" s="26">
+      <c r="K75" s="23">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
-      <c r="L75" s="27">
+      <c r="L75" s="24">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
-      <c r="M75" s="26">
+      <c r="M75" s="23">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
-      <c r="N75" s="26">
+      <c r="N75" s="23">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
-      <c r="O75" s="26">
+      <c r="O75" s="23">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
-      <c r="P75" s="26">
+      <c r="P75" s="23">
         <f t="shared" si="13"/>
         <v>2500000</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>83</v>
       </c>
@@ -5070,7 +5920,7 @@
       <c r="O76" s="5"/>
       <c r="P76" s="5"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -5120,7 +5970,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>85</v>
       </c>
@@ -5170,7 +6020,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>86</v>
       </c>
@@ -5211,7 +6061,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>87</v>
       </c>
@@ -5228,29 +6078,29 @@
       <c r="I80" s="7">
         <v>200000</v>
       </c>
-      <c r="J80" s="15">
+      <c r="J80" s="12">
         <v>200000</v>
       </c>
-      <c r="K80" s="15">
+      <c r="K80" s="12">
         <v>200000</v>
       </c>
       <c r="L80" s="7">
         <v>200000</v>
       </c>
-      <c r="M80" s="15">
+      <c r="M80" s="12">
         <v>200000</v>
       </c>
-      <c r="N80" s="15">
+      <c r="N80" s="12">
         <v>200000</v>
       </c>
-      <c r="O80" s="15">
+      <c r="O80" s="12">
         <v>200000</v>
       </c>
-      <c r="P80" s="15">
+      <c r="P80" s="12">
         <v>200000</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:17">
       <c r="A81" t="s">
         <v>88</v>
       </c>
@@ -5300,7 +6150,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:17">
       <c r="A82" t="s">
         <v>89</v>
       </c>
@@ -5350,7 +6200,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:17" ht="18.5" thickBot="1">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -5372,319 +6222,319 @@
       <c r="O83" s="5"/>
       <c r="P83" s="5"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="21" t="s">
+    <row r="84" spans="1:17">
+      <c r="A84" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B84" s="22">
+      <c r="B84" s="19">
         <f>SUM(B77:B82)</f>
         <v>2937465</v>
       </c>
-      <c r="C84" s="26">
+      <c r="C84" s="23">
         <f>SUM(C77:C83)</f>
         <v>3770000</v>
       </c>
-      <c r="D84" s="26">
+      <c r="D84" s="23">
         <f>SUM(D77:D82)</f>
         <v>1470000</v>
       </c>
-      <c r="E84" s="26">
+      <c r="E84" s="23">
         <f t="shared" ref="E84:P84" si="14">SUM(E77:E82)</f>
         <v>1320000</v>
       </c>
-      <c r="F84" s="26">
+      <c r="F84" s="23">
         <f t="shared" si="14"/>
         <v>2320000</v>
       </c>
-      <c r="G84" s="26">
+      <c r="G84" s="23">
         <f t="shared" si="14"/>
         <v>1620000</v>
       </c>
-      <c r="H84" s="26">
+      <c r="H84" s="23">
         <f t="shared" si="14"/>
         <v>1650000</v>
       </c>
-      <c r="I84" s="29">
+      <c r="I84" s="26">
         <f t="shared" si="14"/>
         <v>1650000</v>
       </c>
-      <c r="J84" s="26">
+      <c r="J84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="K84" s="26">
+      <c r="K84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="L84" s="29">
+      <c r="L84" s="26">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="M84" s="26">
+      <c r="M84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="N84" s="26">
+      <c r="N84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="O84" s="26">
+      <c r="O84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
-      <c r="P84" s="26">
+      <c r="P84" s="23">
         <f t="shared" si="14"/>
         <v>1850000</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="30" t="s">
+    <row r="85" spans="1:17">
+      <c r="A85" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B85" s="22"/>
-      <c r="C85" s="27">
+      <c r="B85" s="19"/>
+      <c r="C85" s="24">
         <f>C26</f>
         <v>42200000</v>
       </c>
-      <c r="D85" s="27">
+      <c r="D85" s="24">
         <f t="shared" ref="D85:P85" si="15">D26</f>
         <v>36335000</v>
       </c>
-      <c r="E85" s="27">
+      <c r="E85" s="24">
         <f t="shared" si="15"/>
         <v>35400000</v>
       </c>
-      <c r="F85" s="27">
+      <c r="F85" s="24">
         <f t="shared" si="15"/>
         <v>39800000</v>
       </c>
-      <c r="G85" s="27">
+      <c r="G85" s="24">
         <f t="shared" si="15"/>
         <v>47900000</v>
       </c>
-      <c r="H85" s="27">
+      <c r="H85" s="24">
         <f t="shared" si="15"/>
         <v>41300000</v>
       </c>
-      <c r="I85" s="31">
+      <c r="I85" s="28">
         <f t="shared" si="15"/>
         <v>46300000</v>
       </c>
-      <c r="J85" s="27">
+      <c r="J85" s="24">
         <f t="shared" si="15"/>
         <v>46300000</v>
       </c>
-      <c r="K85" s="27">
+      <c r="K85" s="24">
         <f t="shared" si="15"/>
         <v>49050000</v>
       </c>
-      <c r="L85" s="31">
+      <c r="L85" s="28">
         <f t="shared" si="15"/>
         <v>51150000</v>
       </c>
-      <c r="M85" s="27">
+      <c r="M85" s="24">
         <f t="shared" si="15"/>
         <v>54350000</v>
       </c>
-      <c r="N85" s="27">
+      <c r="N85" s="24">
         <f t="shared" si="15"/>
         <v>55100000</v>
       </c>
-      <c r="O85" s="27">
+      <c r="O85" s="24">
         <f t="shared" si="15"/>
         <v>56100000</v>
       </c>
-      <c r="P85" s="27">
+      <c r="P85" s="24">
         <f t="shared" si="15"/>
         <v>55100000</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="30" t="s">
+    <row r="86" spans="1:17">
+      <c r="A86" s="27" t="s">
         <v>92</v>
       </c>
-      <c r="B86" s="32"/>
-      <c r="C86" s="33">
+      <c r="B86" s="29"/>
+      <c r="C86" s="30">
         <f>C38+C51+C59+C66+C70+C75+C84</f>
         <v>42026947</v>
       </c>
-      <c r="D86" s="34">
+      <c r="D86" s="31">
         <f t="shared" ref="D86:P86" si="16">D38+D51+D59+D66+D70+D75+D84</f>
         <v>39202800</v>
       </c>
-      <c r="E86" s="34">
+      <c r="E86" s="31">
         <f t="shared" si="16"/>
         <v>40457000</v>
       </c>
-      <c r="F86" s="34">
+      <c r="F86" s="31">
         <f t="shared" si="16"/>
         <v>39028077.700000003</v>
       </c>
-      <c r="G86" s="34">
+      <c r="G86" s="31">
         <f t="shared" si="16"/>
         <v>40110000</v>
       </c>
-      <c r="H86" s="34">
+      <c r="H86" s="31">
         <f t="shared" si="16"/>
         <v>38550000</v>
       </c>
-      <c r="I86" s="35">
+      <c r="I86" s="32">
         <f t="shared" si="16"/>
         <v>40875000</v>
       </c>
-      <c r="J86" s="34">
+      <c r="J86" s="31">
         <f t="shared" si="16"/>
         <v>40880000</v>
       </c>
-      <c r="K86" s="34">
+      <c r="K86" s="31">
         <f t="shared" si="16"/>
         <v>49630000</v>
       </c>
-      <c r="L86" s="35">
+      <c r="L86" s="32">
         <f t="shared" si="16"/>
         <v>43270000</v>
       </c>
-      <c r="M86" s="34">
+      <c r="M86" s="31">
         <f t="shared" si="16"/>
         <v>47230000</v>
       </c>
-      <c r="N86" s="34">
+      <c r="N86" s="31">
         <f t="shared" si="16"/>
         <v>47805000</v>
       </c>
-      <c r="O86" s="34">
+      <c r="O86" s="31">
         <f t="shared" si="16"/>
         <v>48405000</v>
       </c>
-      <c r="P86" s="34">
+      <c r="P86" s="31">
         <f t="shared" si="16"/>
         <v>55805000</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="30" t="s">
+    <row r="87" spans="1:17">
+      <c r="A87" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="B87" s="32"/>
-      <c r="C87" s="36">
+      <c r="B87" s="29"/>
+      <c r="C87" s="33">
         <f>C26/1.1</f>
         <v>38363636.36363636</v>
       </c>
-      <c r="D87" s="27">
+      <c r="D87" s="24">
         <f t="shared" ref="D87:N87" si="17">D26/1.1</f>
         <v>33031818.18181818</v>
       </c>
-      <c r="E87" s="27">
+      <c r="E87" s="24">
         <f t="shared" si="17"/>
         <v>32181818.18181818</v>
       </c>
-      <c r="F87" s="27">
+      <c r="F87" s="24">
         <f t="shared" si="17"/>
         <v>36181818.18181818</v>
       </c>
-      <c r="G87" s="27">
+      <c r="G87" s="24">
         <f t="shared" si="17"/>
         <v>43545454.545454539</v>
       </c>
-      <c r="H87" s="27">
+      <c r="H87" s="24">
         <f t="shared" si="17"/>
         <v>37545454.545454539</v>
       </c>
-      <c r="I87" s="31">
+      <c r="I87" s="28">
         <f t="shared" si="17"/>
         <v>42090909.090909086</v>
       </c>
-      <c r="J87" s="27">
+      <c r="J87" s="24">
         <f t="shared" si="17"/>
         <v>42090909.090909086</v>
       </c>
-      <c r="K87" s="27">
+      <c r="K87" s="24">
         <f t="shared" si="17"/>
         <v>44590909.090909086</v>
       </c>
-      <c r="L87" s="31">
+      <c r="L87" s="28">
         <f t="shared" si="17"/>
         <v>46499999.999999993</v>
       </c>
-      <c r="M87" s="27">
+      <c r="M87" s="24">
         <f t="shared" si="17"/>
         <v>49409090.909090906</v>
       </c>
-      <c r="N87" s="27">
+      <c r="N87" s="24">
         <f t="shared" si="17"/>
         <v>50090909.090909086</v>
       </c>
-      <c r="O87" s="27">
+      <c r="O87" s="24">
         <f>O85/1.1</f>
         <v>50999999.999999993</v>
       </c>
-      <c r="P87" s="27">
+      <c r="P87" s="24">
         <f>P85/1.1</f>
         <v>50090909.090909086</v>
       </c>
-      <c r="Q87" s="14">
+      <c r="Q87" s="11">
         <f>SUM(E87:P87)</f>
         <v>525318181.81818175</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="37" t="s">
+    <row r="88" spans="1:17">
+      <c r="A88" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="B88" s="32"/>
-      <c r="C88" s="38">
+      <c r="B88" s="29"/>
+      <c r="C88" s="35">
         <f>C86-2500000</f>
         <v>39526947</v>
       </c>
-      <c r="D88" s="26">
+      <c r="D88" s="23">
         <f>D86-((D85-D87)-1600000)</f>
         <v>37499618.18181818</v>
       </c>
-      <c r="E88" s="26">
+      <c r="E88" s="23">
         <f>E86-((E85-E87)-1600000)</f>
         <v>38838818.18181818</v>
       </c>
-      <c r="F88" s="26">
+      <c r="F88" s="23">
         <f>F86-((F85-F87)-1600000)</f>
         <v>37009895.881818183</v>
       </c>
-      <c r="G88" s="26">
+      <c r="G88" s="23">
         <f t="shared" ref="G88:P88" si="18">G86-((G85-G87)-1600000)</f>
         <v>37355454.545454539</v>
       </c>
-      <c r="H88" s="26">
+      <c r="H88" s="23">
         <f t="shared" si="18"/>
         <v>36395454.545454539</v>
       </c>
-      <c r="I88" s="39">
+      <c r="I88" s="36">
         <f t="shared" si="18"/>
         <v>38265909.090909086</v>
       </c>
-      <c r="J88" s="26">
+      <c r="J88" s="23">
         <f t="shared" si="18"/>
         <v>38270909.090909086</v>
       </c>
-      <c r="K88" s="26">
+      <c r="K88" s="23">
         <f t="shared" si="18"/>
         <v>46770909.090909086</v>
       </c>
-      <c r="L88" s="31">
+      <c r="L88" s="28">
         <f t="shared" si="18"/>
         <v>40219999.999999993</v>
       </c>
-      <c r="M88" s="26">
+      <c r="M88" s="23">
         <f t="shared" si="18"/>
         <v>43889090.909090906</v>
       </c>
-      <c r="N88" s="26">
+      <c r="N88" s="23">
         <f t="shared" si="18"/>
         <v>44395909.090909086</v>
       </c>
-      <c r="O88" s="26">
+      <c r="O88" s="23">
         <f t="shared" si="18"/>
         <v>44904999.999999993</v>
       </c>
-      <c r="P88" s="26">
+      <c r="P88" s="23">
         <f t="shared" si="18"/>
         <v>52395909.090909086</v>
       </c>
@@ -5692,140 +6542,140 @@
         <v>95</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="30" t="s">
+    <row r="89" spans="1:17">
+      <c r="A89" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B89" s="32"/>
-      <c r="C89" s="40">
+      <c r="B89" s="29"/>
+      <c r="C89" s="37">
         <f>C87-C88</f>
         <v>-1163310.6363636404</v>
       </c>
-      <c r="D89" s="27">
+      <c r="D89" s="24">
         <f t="shared" ref="D89:P89" si="19">D87-D88</f>
         <v>-4467800</v>
       </c>
-      <c r="E89" s="27">
+      <c r="E89" s="24">
         <f t="shared" si="19"/>
         <v>-6657000</v>
       </c>
-      <c r="F89" s="27">
+      <c r="F89" s="24">
         <f t="shared" si="19"/>
         <v>-828077.70000000298</v>
       </c>
-      <c r="G89" s="27">
+      <c r="G89" s="24">
         <f t="shared" si="19"/>
         <v>6190000</v>
       </c>
-      <c r="H89" s="27">
+      <c r="H89" s="24">
         <f t="shared" si="19"/>
         <v>1150000</v>
       </c>
-      <c r="I89" s="31">
+      <c r="I89" s="28">
         <f t="shared" si="19"/>
         <v>3825000</v>
       </c>
-      <c r="J89" s="27">
+      <c r="J89" s="24">
         <f t="shared" si="19"/>
         <v>3820000</v>
       </c>
-      <c r="K89" s="27">
+      <c r="K89" s="24">
         <f t="shared" si="19"/>
         <v>-2180000</v>
       </c>
-      <c r="L89" s="31">
+      <c r="L89" s="28">
         <f t="shared" si="19"/>
         <v>6280000</v>
       </c>
-      <c r="M89" s="27">
+      <c r="M89" s="24">
         <f t="shared" si="19"/>
         <v>5520000</v>
       </c>
-      <c r="N89" s="27">
+      <c r="N89" s="24">
         <f t="shared" si="19"/>
         <v>5695000</v>
       </c>
-      <c r="O89" s="27">
+      <c r="O89" s="24">
         <f t="shared" si="19"/>
         <v>6095000</v>
       </c>
-      <c r="P89" s="27">
+      <c r="P89" s="24">
         <f t="shared" si="19"/>
         <v>-2305000</v>
       </c>
-      <c r="Q89" s="14">
+      <c r="Q89" s="11">
         <f>SUM(E89:P89)</f>
         <v>26604922.299999997</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="37" t="s">
+    <row r="90" spans="1:17">
+      <c r="A90" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="32"/>
-      <c r="C90" s="38">
+      <c r="B90" s="29"/>
+      <c r="C90" s="35">
         <f>C87*0.1</f>
         <v>3836363.6363636362</v>
       </c>
-      <c r="D90" s="26">
+      <c r="D90" s="23">
         <f t="shared" ref="D90:P90" si="20">D87*0.1</f>
         <v>3303181.8181818184</v>
       </c>
-      <c r="E90" s="26">
+      <c r="E90" s="23">
         <f t="shared" si="20"/>
         <v>3218181.8181818184</v>
       </c>
-      <c r="F90" s="26">
+      <c r="F90" s="23">
         <f t="shared" si="20"/>
         <v>3618181.8181818184</v>
       </c>
-      <c r="G90" s="26">
+      <c r="G90" s="23">
         <f t="shared" si="20"/>
         <v>4354545.4545454541</v>
       </c>
-      <c r="H90" s="26">
+      <c r="H90" s="23">
         <f t="shared" si="20"/>
         <v>3754545.4545454541</v>
       </c>
-      <c r="I90" s="39">
+      <c r="I90" s="36">
         <f t="shared" si="20"/>
         <v>4209090.9090909092</v>
       </c>
-      <c r="J90" s="26">
+      <c r="J90" s="23">
         <f t="shared" si="20"/>
         <v>4209090.9090909092</v>
       </c>
-      <c r="K90" s="26">
+      <c r="K90" s="23">
         <f t="shared" si="20"/>
         <v>4459090.9090909092</v>
       </c>
-      <c r="L90" s="31">
+      <c r="L90" s="28">
         <f t="shared" si="20"/>
         <v>4649999.9999999991</v>
       </c>
-      <c r="M90" s="26">
+      <c r="M90" s="23">
         <f t="shared" si="20"/>
         <v>4940909.0909090908</v>
       </c>
-      <c r="N90" s="26">
+      <c r="N90" s="23">
         <f t="shared" si="20"/>
         <v>5009090.9090909092</v>
       </c>
-      <c r="O90" s="26">
+      <c r="O90" s="23">
         <f t="shared" si="20"/>
         <v>5100000</v>
       </c>
-      <c r="P90" s="26">
+      <c r="P90" s="23">
         <f t="shared" si="20"/>
         <v>5009090.9090909092</v>
       </c>
-      <c r="Q90" s="14">
+      <c r="Q90" s="11">
         <f>SUM(E90:P90)</f>
         <v>52531818.18181818</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A91" s="37" t="s">
+    <row r="91" spans="1:17" ht="18.5" thickBot="1">
+      <c r="A91" s="34" t="s">
         <v>98</v>
       </c>
       <c r="B91" s="5"/>
@@ -5835,13 +6685,13 @@
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
-      <c r="I91" s="41">
+      <c r="I91" s="38">
         <f>I89/I87</f>
         <v>9.087473002159828E-2</v>
       </c>
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
-      <c r="L91" s="41">
+      <c r="L91" s="38">
         <f>L89/L87</f>
         <v>0.13505376344086023</v>
       </c>
@@ -5850,7 +6700,7 @@
       <c r="O91" s="5"/>
       <c r="P91" s="5"/>
     </row>
-    <row r="92" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:17" ht="18.5" thickBot="1">
       <c r="A92" t="s">
         <v>99</v>
       </c>
@@ -5870,560 +6720,560 @@
       <c r="O92" s="5"/>
       <c r="P92" s="5"/>
     </row>
-    <row r="93" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A93" s="42" t="s">
+    <row r="93" spans="1:17" ht="18.5" thickBot="1">
+      <c r="A93" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="43">
+      <c r="B93" s="40">
         <f t="shared" ref="B93:J93" si="21">B26-B38-B51-B59-B66-B70-B75-B84</f>
         <v>3063496</v>
       </c>
-      <c r="C93" s="43">
+      <c r="C93" s="40">
         <f t="shared" si="21"/>
         <v>173053</v>
       </c>
-      <c r="D93" s="43">
+      <c r="D93" s="40">
         <f t="shared" si="21"/>
         <v>-2867800</v>
       </c>
-      <c r="E93" s="43">
+      <c r="E93" s="40">
         <f t="shared" si="21"/>
         <v>-5057000</v>
       </c>
-      <c r="F93" s="43">
+      <c r="F93" s="40">
         <f t="shared" si="21"/>
         <v>771922.30000000075</v>
       </c>
-      <c r="G93" s="43">
+      <c r="G93" s="40">
         <f t="shared" si="21"/>
         <v>7790000</v>
       </c>
-      <c r="H93" s="43">
+      <c r="H93" s="40">
         <f t="shared" si="21"/>
         <v>2750000</v>
       </c>
-      <c r="I93" s="44">
+      <c r="I93" s="41">
         <f t="shared" si="21"/>
         <v>5425000</v>
       </c>
-      <c r="J93" s="43">
+      <c r="J93" s="40">
         <f t="shared" si="21"/>
         <v>5420000</v>
       </c>
-      <c r="K93" s="43">
+      <c r="K93" s="40">
         <f>K26-K38-K51-K59-K66-K69-K75-K84</f>
         <v>170000</v>
       </c>
-      <c r="L93" s="44">
+      <c r="L93" s="41">
         <f>L26-L38-L51-L59-L66-L70-L75-L84</f>
         <v>7880000</v>
       </c>
-      <c r="M93" s="43">
+      <c r="M93" s="40">
         <f>M26-M38-M51-M59-M66-M70-M75-M84</f>
         <v>7120000</v>
       </c>
-      <c r="N93" s="43">
+      <c r="N93" s="40">
         <f>N26-N38-N51-N59-N66-N70-N75-N84</f>
         <v>7295000</v>
       </c>
-      <c r="O93" s="43">
+      <c r="O93" s="40">
         <f>O26-O38-O51-O59-O66-O70-O75-O84</f>
         <v>7695000</v>
       </c>
-      <c r="P93" s="43">
+      <c r="P93" s="40">
         <f>P26-P38-P51-P59-P66-P70-P75-P84</f>
         <v>-705000</v>
       </c>
-      <c r="Q93" s="45">
+      <c r="Q93" s="42">
         <f>SUM(E93:P93)</f>
         <v>46554922.299999997</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:17">
       <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="46">
+      <c r="B94" s="43">
         <f t="shared" ref="B94:Q94" si="22">B93/B26</f>
         <v>6.6434698271249135E-2</v>
       </c>
-      <c r="C94" s="46">
+      <c r="C94" s="43">
         <f t="shared" si="22"/>
         <v>4.1007819905213268E-3</v>
       </c>
-      <c r="D94" s="46">
+      <c r="D94" s="43">
         <f t="shared" si="22"/>
         <v>-7.8926654740608226E-2</v>
       </c>
-      <c r="E94" s="46">
+      <c r="E94" s="43">
         <f t="shared" si="22"/>
         <v>-0.14285310734463277</v>
       </c>
-      <c r="F94" s="46">
+      <c r="F94" s="43">
         <f t="shared" si="22"/>
         <v>1.9395032663316603E-2</v>
       </c>
-      <c r="G94" s="46">
+      <c r="G94" s="43">
         <f t="shared" si="22"/>
         <v>0.16263048016701462</v>
       </c>
-      <c r="H94" s="46">
+      <c r="H94" s="43">
         <f t="shared" si="22"/>
         <v>6.6585956416464892E-2</v>
       </c>
-      <c r="I94" s="47">
+      <c r="I94" s="44">
         <f t="shared" si="22"/>
         <v>0.117170626349892</v>
       </c>
-      <c r="J94" s="46">
+      <c r="J94" s="43">
         <f t="shared" si="22"/>
         <v>0.11706263498920086</v>
       </c>
-      <c r="K94" s="46">
+      <c r="K94" s="43">
         <f t="shared" si="22"/>
         <v>3.4658511722731908E-3</v>
       </c>
-      <c r="L94" s="47">
+      <c r="L94" s="44">
         <f t="shared" si="22"/>
         <v>0.15405669599217986</v>
       </c>
-      <c r="M94" s="46">
+      <c r="M94" s="43">
         <f t="shared" si="22"/>
         <v>0.13100275988960441</v>
       </c>
-      <c r="N94" s="46">
+      <c r="N94" s="43">
         <f t="shared" si="22"/>
         <v>0.13239564428312159</v>
       </c>
-      <c r="O94" s="46">
+      <c r="O94" s="43">
         <f t="shared" si="22"/>
         <v>0.13716577540106953</v>
       </c>
-      <c r="P94" s="46">
+      <c r="P94" s="43">
         <f t="shared" si="22"/>
         <v>-1.2794918330308529E-2</v>
       </c>
-      <c r="Q94" s="46">
+      <c r="Q94" s="43">
         <f t="shared" si="22"/>
         <v>8.186920302470764E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="42" t="s">
+    <row r="95" spans="1:17">
+      <c r="A95" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B95" s="43">
+      <c r="B95" s="40">
         <f t="shared" ref="B95:P95" si="23">B26-B38-B51-B59-B66-B73</f>
         <v>7759917</v>
       </c>
-      <c r="C95" s="43">
+      <c r="C95" s="40">
         <f t="shared" si="23"/>
         <v>5943053</v>
       </c>
-      <c r="D95" s="43">
+      <c r="D95" s="40">
         <f t="shared" si="23"/>
         <v>2602200</v>
       </c>
-      <c r="E95" s="43">
+      <c r="E95" s="40">
         <f t="shared" si="23"/>
         <v>-1737000</v>
       </c>
-      <c r="F95" s="43">
+      <c r="F95" s="40">
         <f t="shared" si="23"/>
         <v>3787012.3000000007</v>
       </c>
-      <c r="G95" s="43">
+      <c r="G95" s="40">
         <f t="shared" si="23"/>
         <v>10160000</v>
       </c>
-      <c r="H95" s="43">
+      <c r="H95" s="40">
         <f t="shared" si="23"/>
         <v>5150000</v>
       </c>
-      <c r="I95" s="48">
+      <c r="I95" s="45">
         <f t="shared" si="23"/>
         <v>7825000</v>
       </c>
-      <c r="J95" s="43">
+      <c r="J95" s="40">
         <f t="shared" si="23"/>
         <v>8020000</v>
       </c>
-      <c r="K95" s="43">
+      <c r="K95" s="40">
         <f t="shared" si="23"/>
         <v>9020000</v>
       </c>
-      <c r="L95" s="48">
+      <c r="L95" s="45">
         <f t="shared" si="23"/>
         <v>10480000</v>
       </c>
-      <c r="M95" s="43">
+      <c r="M95" s="40">
         <f t="shared" si="23"/>
         <v>9720000</v>
       </c>
-      <c r="N95" s="43">
+      <c r="N95" s="40">
         <f t="shared" si="23"/>
         <v>9895000</v>
       </c>
-      <c r="O95" s="43">
+      <c r="O95" s="40">
         <f t="shared" si="23"/>
         <v>10295000</v>
       </c>
-      <c r="P95" s="43">
+      <c r="P95" s="40">
         <f t="shared" si="23"/>
         <v>9895000</v>
       </c>
-      <c r="Q95" s="45">
+      <c r="Q95" s="42">
         <f>SUM(E95:P95)</f>
         <v>92510012.299999997</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:17">
       <c r="A96" t="s">
         <v>101</v>
       </c>
-      <c r="B96" s="46">
+      <c r="B96" s="43">
         <f t="shared" ref="B96:Q96" si="24">B95/B26</f>
         <v>0.16828086098527198</v>
       </c>
-      <c r="C96" s="46">
+      <c r="C96" s="43">
         <f t="shared" si="24"/>
         <v>0.14083063981042654</v>
       </c>
-      <c r="D96" s="46">
+      <c r="D96" s="43">
         <f t="shared" si="24"/>
         <v>7.161689830741709E-2</v>
       </c>
-      <c r="E96" s="46">
+      <c r="E96" s="43">
         <f t="shared" si="24"/>
         <v>-4.9067796610169488E-2</v>
       </c>
-      <c r="F96" s="46">
+      <c r="F96" s="43">
         <f t="shared" si="24"/>
         <v>9.5151062814070375E-2</v>
       </c>
-      <c r="G96" s="46">
+      <c r="G96" s="43">
         <f t="shared" si="24"/>
         <v>0.21210855949895616</v>
       </c>
-      <c r="H96" s="46">
+      <c r="H96" s="43">
         <f t="shared" si="24"/>
         <v>0.12469733656174334</v>
       </c>
-      <c r="I96" s="47">
+      <c r="I96" s="44">
         <f t="shared" si="24"/>
         <v>0.16900647948164146</v>
       </c>
-      <c r="J96" s="46">
+      <c r="J96" s="43">
         <f t="shared" si="24"/>
         <v>0.1732181425485961</v>
       </c>
-      <c r="K96" s="46">
+      <c r="K96" s="43">
         <f t="shared" si="24"/>
         <v>0.1838939857288481</v>
       </c>
-      <c r="L96" s="47">
+      <c r="L96" s="44">
         <f t="shared" si="24"/>
         <v>0.20488758553274683</v>
       </c>
-      <c r="M96" s="46">
+      <c r="M96" s="43">
         <f t="shared" si="24"/>
         <v>0.17884084636614536</v>
       </c>
-      <c r="N96" s="46">
+      <c r="N96" s="43">
         <f t="shared" si="24"/>
         <v>0.17958257713248638</v>
       </c>
-      <c r="O96" s="46">
+      <c r="O96" s="43">
         <f t="shared" si="24"/>
         <v>0.18351158645276291</v>
       </c>
-      <c r="P96" s="46">
+      <c r="P96" s="43">
         <f t="shared" si="24"/>
         <v>0.17958257713248638</v>
       </c>
-      <c r="Q96" s="46">
+      <c r="Q96" s="43">
         <f t="shared" si="24"/>
         <v>0.16268357038600192</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A97" s="42" t="s">
+    <row r="97" spans="1:17" hidden="1">
+      <c r="A97" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B97" s="43">
+      <c r="B97" s="40">
         <f>B23-B38-B51-B59-B66-B70-B74-B84</f>
         <v>-64562</v>
       </c>
-      <c r="C97" s="43">
+      <c r="C97" s="40">
         <f>C23-C38-C51-C59-C66-C70-C68-C84</f>
         <v>-3896947</v>
       </c>
-      <c r="D97" s="43">
+      <c r="D97" s="40">
         <f t="shared" ref="D97:J97" si="25">D23-D38-D51-D59-D66-D70-D74-D84</f>
         <v>-4802800</v>
       </c>
-      <c r="E97" s="43">
+      <c r="E97" s="40">
         <f t="shared" si="25"/>
         <v>-6057000</v>
       </c>
-      <c r="F97" s="43">
+      <c r="F97" s="40">
         <f t="shared" si="25"/>
         <v>1371922.3000000007</v>
       </c>
-      <c r="G97" s="43">
+      <c r="G97" s="40">
         <f t="shared" si="25"/>
         <v>7790000</v>
       </c>
-      <c r="H97" s="43">
+      <c r="H97" s="40">
         <f t="shared" si="25"/>
         <v>2750000</v>
       </c>
-      <c r="I97" s="48">
+      <c r="I97" s="45">
         <f t="shared" si="25"/>
         <v>5625000</v>
       </c>
-      <c r="J97" s="43">
+      <c r="J97" s="40">
         <f t="shared" si="25"/>
         <v>5620000</v>
       </c>
-      <c r="K97" s="43" t="e">
+      <c r="K97" s="40" t="e">
         <f>K23-K38-K51-K59-K66-K69-K74-K84</f>
         <v>#VALUE!</v>
       </c>
-      <c r="L97" s="48">
+      <c r="L97" s="45">
         <f>L23-L38-L51-L59-L66-L70-L74-L84</f>
         <v>8830000</v>
       </c>
-      <c r="M97" s="43">
+      <c r="M97" s="40">
         <f>M23-M38-M51-M59-M66-M70-M74-M84</f>
         <v>8070000</v>
       </c>
-      <c r="N97" s="43">
+      <c r="N97" s="40">
         <f>N23-N38-N51-N59-N66-N70-N74-N84</f>
         <v>8495000</v>
       </c>
-      <c r="O97" s="43">
+      <c r="O97" s="40">
         <f>O23-O38-O51-O59-O66-O70-O74-O84</f>
         <v>8895000</v>
       </c>
-      <c r="P97" s="43">
+      <c r="P97" s="40">
         <f>P23-P38-P51-P59-P66-P70-P74-P84</f>
         <v>495000</v>
       </c>
-      <c r="Q97" s="45" t="e">
+      <c r="Q97" s="42" t="e">
         <f>SUM(E97:P97)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:17" ht="19" hidden="1" customHeight="1">
       <c r="A98" t="s">
         <v>101</v>
       </c>
-      <c r="B98" s="46">
+      <c r="B98" s="43">
         <f t="shared" ref="B98:Q98" si="26">B97/B23</f>
         <v>-1.5620666101088321E-3</v>
       </c>
-      <c r="C98" s="46">
+      <c r="C98" s="43">
         <f t="shared" si="26"/>
         <v>-0.10069630490956072</v>
       </c>
-      <c r="D98" s="46">
+      <c r="D98" s="43">
         <f t="shared" si="26"/>
         <v>-0.14379640718562875</v>
       </c>
-      <c r="E98" s="46">
+      <c r="E98" s="43">
         <f t="shared" si="26"/>
         <v>-0.18694444444444444</v>
       </c>
-      <c r="F98" s="46">
+      <c r="F98" s="43">
         <f t="shared" si="26"/>
         <v>3.7586912328767146E-2</v>
       </c>
-      <c r="G98" s="46">
+      <c r="G98" s="43">
         <f t="shared" si="26"/>
         <v>0.16971677559912854</v>
       </c>
-      <c r="H98" s="46">
+      <c r="H98" s="43">
         <f t="shared" si="26"/>
         <v>6.9974554707379136E-2</v>
       </c>
-      <c r="I98" s="47">
+      <c r="I98" s="44">
         <f t="shared" si="26"/>
         <v>0.12640449438202248</v>
       </c>
-      <c r="J98" s="46">
+      <c r="J98" s="43">
         <f t="shared" si="26"/>
         <v>0.12629213483146068</v>
       </c>
-      <c r="K98" s="46" t="e">
+      <c r="K98" s="43" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
-      <c r="L98" s="47">
+      <c r="L98" s="44">
         <f t="shared" si="26"/>
         <v>0.17802419354838708</v>
       </c>
-      <c r="M98" s="46">
+      <c r="M98" s="43">
         <f t="shared" si="26"/>
         <v>0.15284090909090908</v>
       </c>
-      <c r="N98" s="46">
+      <c r="N98" s="43">
         <f t="shared" si="26"/>
         <v>0.15789962825278811</v>
       </c>
-      <c r="O98" s="46">
+      <c r="O98" s="43">
         <f t="shared" si="26"/>
         <v>0.16231751824817517</v>
       </c>
-      <c r="P98" s="46">
+      <c r="P98" s="43">
         <f t="shared" si="26"/>
         <v>9.2007434944237926E-3</v>
       </c>
-      <c r="Q98" s="46" t="e">
+      <c r="Q98" s="43" t="e">
         <f t="shared" si="26"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="42" t="s">
+    <row r="99" spans="1:17" ht="19" hidden="1" customHeight="1">
+      <c r="A99" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="B99" s="43">
+      <c r="B99" s="40">
         <f t="shared" ref="B99:J99" si="27">B23-B38-B51-B59-B66-B70</f>
         <v>4631859</v>
       </c>
-      <c r="C99" s="43">
+      <c r="C99" s="40">
         <f t="shared" si="27"/>
         <v>1873053</v>
       </c>
-      <c r="D99" s="43">
+      <c r="D99" s="40">
         <f t="shared" si="27"/>
         <v>-3332800</v>
       </c>
-      <c r="E99" s="43">
+      <c r="E99" s="40">
         <f t="shared" si="27"/>
         <v>-4737000</v>
       </c>
-      <c r="F99" s="43">
+      <c r="F99" s="40">
         <f t="shared" si="27"/>
         <v>3691922.3000000007</v>
       </c>
-      <c r="G99" s="43">
+      <c r="G99" s="40">
         <f t="shared" si="27"/>
         <v>9410000</v>
       </c>
-      <c r="H99" s="43">
+      <c r="H99" s="40">
         <f t="shared" si="27"/>
         <v>4400000</v>
       </c>
-      <c r="I99" s="48">
+      <c r="I99" s="45">
         <f t="shared" si="27"/>
         <v>7275000</v>
       </c>
-      <c r="J99" s="43">
+      <c r="J99" s="40">
         <f t="shared" si="27"/>
         <v>7470000</v>
       </c>
-      <c r="K99" s="43">
+      <c r="K99" s="40">
         <f>K23-K38-K51-K59-K66-K69</f>
         <v>2970000</v>
       </c>
-      <c r="L99" s="48">
+      <c r="L99" s="45">
         <f>L23-L38-L51-L59-L66-L70</f>
         <v>10680000</v>
       </c>
-      <c r="M99" s="43">
+      <c r="M99" s="40">
         <f>M23-M38-M51-M59-M66-M70</f>
         <v>9920000</v>
       </c>
-      <c r="N99" s="43">
+      <c r="N99" s="40">
         <f>N23-N38-N51-N59-N66-N70</f>
         <v>10345000</v>
       </c>
-      <c r="O99" s="43">
+      <c r="O99" s="40">
         <f>O23-O38-O51-O59-O66-O70</f>
         <v>10745000</v>
       </c>
-      <c r="P99" s="43">
+      <c r="P99" s="40">
         <f>P23-P38-P51-P59-P66-P70</f>
         <v>2345000</v>
       </c>
-      <c r="Q99" s="45">
+      <c r="Q99" s="42">
         <f>SUM(E99:P99)</f>
         <v>74514922.299999997</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="19" hidden="1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:17" ht="19" hidden="1" customHeight="1">
       <c r="A100" t="s">
         <v>101</v>
       </c>
-      <c r="B100" s="46">
+      <c r="B100" s="43">
         <f t="shared" ref="B100:Q100" si="28">B99/B23</f>
         <v>0.11206704077680502</v>
       </c>
-      <c r="C100" s="46">
+      <c r="C100" s="43">
         <f t="shared" si="28"/>
         <v>4.8399302325581393E-2</v>
       </c>
-      <c r="D100" s="46">
+      <c r="D100" s="43">
         <f t="shared" si="28"/>
         <v>-9.9784431137724547E-2</v>
       </c>
-      <c r="E100" s="46">
+      <c r="E100" s="43">
         <f t="shared" si="28"/>
         <v>-0.1462037037037037</v>
       </c>
-      <c r="F100" s="46">
+      <c r="F100" s="43">
         <f t="shared" si="28"/>
         <v>0.10114855616438358</v>
       </c>
-      <c r="G100" s="46">
+      <c r="G100" s="43">
         <f t="shared" si="28"/>
         <v>0.20501089324618738</v>
       </c>
-      <c r="H100" s="46">
+      <c r="H100" s="43">
         <f t="shared" si="28"/>
         <v>0.11195928753180662</v>
       </c>
-      <c r="I100" s="47">
+      <c r="I100" s="44">
         <f t="shared" si="28"/>
         <v>0.16348314606741574</v>
       </c>
-      <c r="J100" s="46">
+      <c r="J100" s="43">
         <f t="shared" si="28"/>
         <v>0.16786516853932584</v>
       </c>
-      <c r="K100" s="46">
+      <c r="K100" s="43">
         <f t="shared" si="28"/>
         <v>6.252631578947368E-2</v>
       </c>
-      <c r="L100" s="47">
+      <c r="L100" s="44">
         <f t="shared" si="28"/>
         <v>0.2153225806451613</v>
       </c>
-      <c r="M100" s="46">
+      <c r="M100" s="43">
         <f t="shared" si="28"/>
         <v>0.18787878787878787</v>
       </c>
-      <c r="N100" s="46">
+      <c r="N100" s="43">
         <f t="shared" si="28"/>
         <v>0.19228624535315986</v>
       </c>
-      <c r="O100" s="46">
+      <c r="O100" s="43">
         <f t="shared" si="28"/>
         <v>0.19607664233576641</v>
       </c>
-      <c r="P100" s="46">
+      <c r="P100" s="43">
         <f t="shared" si="28"/>
         <v>4.3587360594795538E-2</v>
       </c>
-      <c r="Q100" s="46">
+      <c r="Q100" s="43">
         <f t="shared" si="28"/>
         <v>0.13513769006166121</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="49" t="s">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="19" customHeight="1">
+      <c r="A101" s="46" t="s">
         <v>105</v>
       </c>
       <c r="D101" s="5">
@@ -6450,13 +7300,13 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:17" ht="19" customHeight="1">
       <c r="A102" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="46"/>
-      <c r="C102" s="46"/>
-      <c r="D102" s="46"/>
+      <c r="B102" s="43"/>
+      <c r="C102" s="43"/>
+      <c r="D102" s="43"/>
       <c r="E102" s="5">
         <f>E93-E101</f>
         <v>-11057000</v>
@@ -6469,14 +7319,14 @@
         <f>G93-G101</f>
         <v>2790000</v>
       </c>
-      <c r="H102" s="46"/>
-      <c r="I102" s="47"/>
+      <c r="H102" s="43"/>
+      <c r="I102" s="44"/>
       <c r="J102" s="5">
         <f>J93-J101</f>
         <v>420000</v>
       </c>
-      <c r="K102" s="46"/>
-      <c r="L102" s="47"/>
+      <c r="K102" s="43"/>
+      <c r="L102" s="44"/>
       <c r="M102" s="5">
         <f>M93-M101</f>
         <v>2120000</v>
@@ -6488,31 +7338,31 @@
         <v>-5705000</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:17" ht="19" customHeight="1">
       <c r="A103" t="s">
         <v>107</v>
       </c>
-      <c r="B103" s="46"/>
-      <c r="C103" s="46"/>
-      <c r="D103" s="46"/>
-      <c r="E103" s="46"/>
-      <c r="F103" s="46"/>
-      <c r="G103" s="46"/>
-      <c r="H103" s="46"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="46"/>
-      <c r="K103" s="46"/>
-      <c r="L103" s="47"/>
+      <c r="B103" s="43"/>
+      <c r="C103" s="43"/>
+      <c r="D103" s="43"/>
+      <c r="E103" s="43"/>
+      <c r="F103" s="43"/>
+      <c r="G103" s="43"/>
+      <c r="H103" s="43"/>
+      <c r="I103" s="44"/>
+      <c r="J103" s="43"/>
+      <c r="K103" s="43"/>
+      <c r="L103" s="44"/>
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
       <c r="P103" s="5"/>
     </row>
-    <row r="104" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:17" ht="19" customHeight="1">
       <c r="A104" t="s">
         <v>108</v>
       </c>
-      <c r="B104" s="46"/>
+      <c r="B104" s="43"/>
       <c r="C104" s="5"/>
       <c r="D104" s="5">
         <f t="shared" ref="D104:P104" si="29">D5-(D5)*0.25-D53-D56</f>
@@ -6567,67 +7417,67 @@
         <v>5320000</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B105" s="46"/>
+    <row r="105" spans="1:17" ht="19" customHeight="1">
+      <c r="B105" s="43"/>
       <c r="C105" s="5"/>
-      <c r="D105" s="46">
+      <c r="D105" s="43">
         <f t="shared" ref="D105:P105" si="30">D104/D5</f>
         <v>0.30333333333333334</v>
       </c>
-      <c r="E105" s="46">
+      <c r="E105" s="43">
         <f t="shared" si="30"/>
         <v>-8.7499999999999994E-2</v>
       </c>
-      <c r="F105" s="46">
+      <c r="F105" s="43">
         <f t="shared" si="30"/>
         <v>0.43733333333333335</v>
       </c>
-      <c r="G105" s="46">
+      <c r="G105" s="43">
         <f t="shared" si="30"/>
         <v>0.22666666666666666</v>
       </c>
-      <c r="H105" s="46">
+      <c r="H105" s="43">
         <f t="shared" si="30"/>
         <v>0.25666666666666665</v>
       </c>
-      <c r="I105" s="47">
+      <c r="I105" s="44">
         <f t="shared" si="30"/>
         <v>0.31470588235294117</v>
       </c>
-      <c r="J105" s="46">
+      <c r="J105" s="43">
         <f t="shared" si="30"/>
         <v>0.25117647058823528</v>
       </c>
-      <c r="K105" s="46">
+      <c r="K105" s="43">
         <f t="shared" si="30"/>
         <v>0.27888888888888891</v>
       </c>
-      <c r="L105" s="47">
+      <c r="L105" s="44">
         <f t="shared" si="30"/>
         <v>0.34</v>
       </c>
-      <c r="M105" s="46">
+      <c r="M105" s="43">
         <f t="shared" si="30"/>
         <v>0.24181818181818182</v>
       </c>
-      <c r="N105" s="46">
+      <c r="N105" s="43">
         <f t="shared" si="30"/>
         <v>0.24181818181818182</v>
       </c>
-      <c r="O105" s="46">
+      <c r="O105" s="43">
         <f t="shared" si="30"/>
         <v>0.24181818181818182</v>
       </c>
-      <c r="P105" s="46">
+      <c r="P105" s="43">
         <f t="shared" si="30"/>
         <v>0.24181818181818182</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:17" ht="19" customHeight="1">
       <c r="A106" t="s">
         <v>109</v>
       </c>
-      <c r="B106" s="46"/>
+      <c r="B106" s="43"/>
       <c r="C106" s="5"/>
       <c r="D106" s="5">
         <f t="shared" ref="D106:P106" si="31">D7-(D7)*0.65</f>
@@ -6682,67 +7532,67 @@
         <v>6300000</v>
       </c>
     </row>
-    <row r="107" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B107" s="46"/>
+    <row r="107" spans="1:17" ht="19" customHeight="1">
+      <c r="B107" s="43"/>
       <c r="C107" s="5"/>
-      <c r="D107" s="46">
+      <c r="D107" s="43">
         <f t="shared" ref="D107:P107" si="32">D106/D7</f>
         <v>0.35</v>
       </c>
-      <c r="E107" s="46">
+      <c r="E107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="F107" s="46">
+      <c r="F107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="G107" s="46">
+      <c r="G107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="H107" s="46">
+      <c r="H107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="I107" s="47">
+      <c r="I107" s="44">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="J107" s="46">
+      <c r="J107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="K107" s="46">
+      <c r="K107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="L107" s="47">
+      <c r="L107" s="44">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="M107" s="46">
+      <c r="M107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="N107" s="46">
+      <c r="N107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="O107" s="46">
+      <c r="O107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
-      <c r="P107" s="46">
+      <c r="P107" s="43">
         <f t="shared" si="32"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:17" ht="19" customHeight="1">
       <c r="A108" t="s">
         <v>110</v>
       </c>
-      <c r="B108" s="46"/>
+      <c r="B108" s="43"/>
       <c r="C108" s="5"/>
       <c r="D108" s="5">
         <f>D9-(D9)*0.3-(D9)*0.35-800000</f>
@@ -6768,11 +7618,11 @@
         <f>I9-(I9)*0.35-(I9)*0.35</f>
         <v>3150000.0000000005</v>
       </c>
-      <c r="J108" s="15">
+      <c r="J108" s="12">
         <f t="shared" ref="J108:P108" si="33">J9-(J9)*0.35-(J9)*0.35</f>
         <v>2700000</v>
       </c>
-      <c r="K108" s="15">
+      <c r="K108" s="12">
         <f t="shared" si="33"/>
         <v>3150000.0000000005</v>
       </c>
@@ -6780,84 +7630,84 @@
         <f t="shared" si="33"/>
         <v>2700000</v>
       </c>
-      <c r="M108" s="15">
+      <c r="M108" s="12">
         <f t="shared" si="33"/>
         <v>3150000.0000000005</v>
       </c>
-      <c r="N108" s="15">
+      <c r="N108" s="12">
         <f t="shared" si="33"/>
         <v>2700000</v>
       </c>
-      <c r="O108" s="15">
+      <c r="O108" s="12">
         <f t="shared" si="33"/>
         <v>3000000</v>
       </c>
-      <c r="P108" s="15">
+      <c r="P108" s="12">
         <f t="shared" si="33"/>
         <v>2700000</v>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B109" s="46"/>
+    <row r="109" spans="1:17" ht="19" customHeight="1">
+      <c r="B109" s="43"/>
       <c r="C109" s="5"/>
-      <c r="D109" s="46">
+      <c r="D109" s="43">
         <f t="shared" ref="D109:P109" si="34">D108/D9</f>
         <v>0.23571428571428571</v>
       </c>
-      <c r="E109" s="46">
+      <c r="E109" s="43">
         <f t="shared" si="34"/>
         <v>0.27727272727272734</v>
       </c>
-      <c r="F109" s="46">
+      <c r="F109" s="43">
         <f t="shared" si="34"/>
         <v>0.25</v>
       </c>
-      <c r="G109" s="46">
+      <c r="G109" s="43">
         <f t="shared" si="34"/>
         <v>0.2804347826086957</v>
       </c>
-      <c r="H109" s="46">
+      <c r="H109" s="43">
         <f t="shared" si="34"/>
         <v>0.26111111111111113</v>
       </c>
-      <c r="I109" s="47">
+      <c r="I109" s="44">
         <f t="shared" si="34"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="J109" s="46">
+      <c r="J109" s="43">
         <f t="shared" si="34"/>
         <v>0.3</v>
       </c>
-      <c r="K109" s="46">
+      <c r="K109" s="43">
         <f t="shared" si="34"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="L109" s="47">
+      <c r="L109" s="44">
         <f t="shared" si="34"/>
         <v>0.3</v>
       </c>
-      <c r="M109" s="46">
+      <c r="M109" s="43">
         <f t="shared" si="34"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="N109" s="46">
+      <c r="N109" s="43">
         <f t="shared" si="34"/>
         <v>0.3</v>
       </c>
-      <c r="O109" s="46">
+      <c r="O109" s="43">
         <f t="shared" si="34"/>
         <v>0.3</v>
       </c>
-      <c r="P109" s="46">
+      <c r="P109" s="43">
         <f t="shared" si="34"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:17" ht="19" customHeight="1">
       <c r="A110" t="s">
         <v>111</v>
       </c>
-      <c r="B110" s="46"/>
+      <c r="B110" s="43"/>
       <c r="C110" s="5"/>
       <c r="D110" s="5">
         <f>D11-(D11)*0.35-(D11)*0.5</f>
@@ -6912,67 +7762,67 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B111" s="46"/>
+    <row r="111" spans="1:17" ht="19" customHeight="1">
+      <c r="B111" s="43"/>
       <c r="C111" s="5"/>
-      <c r="D111" s="46" t="e">
+      <c r="D111" s="43" t="e">
         <f>D110/D11</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E111" s="46">
+      <c r="E111" s="43">
         <f t="shared" ref="E111:O111" si="37">E110/F11</f>
         <v>0.05</v>
       </c>
-      <c r="F111" s="46">
+      <c r="F111" s="43">
         <f t="shared" si="37"/>
         <v>0.05</v>
       </c>
-      <c r="G111" s="46" t="e">
+      <c r="G111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H111" s="46" t="e">
+      <c r="H111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I111" s="47" t="e">
+      <c r="I111" s="44" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J111" s="46" t="e">
+      <c r="J111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K111" s="46" t="e">
+      <c r="K111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L111" s="47" t="e">
+      <c r="L111" s="44" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M111" s="46" t="e">
+      <c r="M111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N111" s="46" t="e">
+      <c r="N111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O111" s="46" t="e">
+      <c r="O111" s="43" t="e">
         <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="P111" s="46" t="e">
+      <c r="P111" s="43" t="e">
         <f>P110/#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="112" spans="1:17" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:17" ht="19" customHeight="1">
       <c r="A112" t="s">
         <v>112</v>
       </c>
-      <c r="B112" s="46"/>
+      <c r="B112" s="43"/>
       <c r="C112" s="5"/>
       <c r="D112" s="5">
         <f t="shared" ref="D112:P112" si="38">D13-(D13)*0.35-(D13)*0.35</f>
@@ -6998,11 +7848,11 @@
         <f t="shared" si="38"/>
         <v>600000</v>
       </c>
-      <c r="J112" s="15">
+      <c r="J112" s="12">
         <f t="shared" si="38"/>
         <v>600000</v>
       </c>
-      <c r="K112" s="15">
+      <c r="K112" s="12">
         <f t="shared" si="38"/>
         <v>600000</v>
       </c>
@@ -7010,15 +7860,15 @@
         <f t="shared" si="38"/>
         <v>600000</v>
       </c>
-      <c r="M112" s="15">
+      <c r="M112" s="12">
         <f t="shared" si="38"/>
         <v>600000</v>
       </c>
-      <c r="N112" s="15">
+      <c r="N112" s="12">
         <f t="shared" si="38"/>
         <v>750000</v>
       </c>
-      <c r="O112" s="15">
+      <c r="O112" s="12">
         <f t="shared" si="38"/>
         <v>750000</v>
       </c>
@@ -7027,67 +7877,67 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="113" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B113" s="46"/>
+    <row r="113" spans="1:16" ht="19" customHeight="1">
+      <c r="B113" s="43"/>
       <c r="C113" s="5"/>
-      <c r="D113" s="46" t="e">
+      <c r="D113" s="43" t="e">
         <f t="shared" ref="D113:P113" si="39">D112/D13</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E113" s="46">
+      <c r="E113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="F113" s="46">
+      <c r="F113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="G113" s="46">
+      <c r="G113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="H113" s="46">
+      <c r="H113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="I113" s="47">
+      <c r="I113" s="44">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="J113" s="46">
+      <c r="J113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="K113" s="46">
+      <c r="K113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="L113" s="47">
+      <c r="L113" s="44">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="M113" s="46">
+      <c r="M113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="N113" s="46">
+      <c r="N113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="O113" s="46">
+      <c r="O113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
-      <c r="P113" s="46">
+      <c r="P113" s="43">
         <f t="shared" si="39"/>
         <v>0.3</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:16" ht="19" customHeight="1">
       <c r="A114" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="46"/>
+      <c r="B114" s="43"/>
       <c r="C114" s="5"/>
       <c r="D114" s="5">
         <f t="shared" ref="D114:P114" si="40">D16-(D16)*0.4</f>
@@ -7142,63 +7992,63 @@
         <v>480000</v>
       </c>
     </row>
-    <row r="115" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="46"/>
+    <row r="115" spans="1:16" ht="19" customHeight="1">
+      <c r="B115" s="43"/>
       <c r="C115" s="5"/>
-      <c r="D115" s="46">
+      <c r="D115" s="43">
         <f t="shared" ref="D115:P115" si="41">D114/D16</f>
         <v>0.6</v>
       </c>
-      <c r="E115" s="46">
+      <c r="E115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="F115" s="46">
+      <c r="F115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="G115" s="46">
+      <c r="G115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="H115" s="46">
+      <c r="H115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="I115" s="47">
+      <c r="I115" s="44">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="J115" s="46">
+      <c r="J115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="K115" s="46">
+      <c r="K115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="L115" s="47">
+      <c r="L115" s="44">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="M115" s="46">
+      <c r="M115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="N115" s="46">
+      <c r="N115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="O115" s="46">
+      <c r="O115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
-      <c r="P115" s="46">
+      <c r="P115" s="43">
         <f t="shared" si="41"/>
         <v>0.6</v>
       </c>
     </row>
-    <row r="116" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:16" ht="19" customHeight="1">
       <c r="A116" t="s">
         <v>114</v>
       </c>
@@ -7257,63 +8107,63 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="117" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:16" ht="19" customHeight="1">
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
-      <c r="D117" s="46" t="e">
+      <c r="D117" s="43" t="e">
         <f>D116/D20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E117" s="46" t="e">
+      <c r="E117" s="43" t="e">
         <f>E116/E20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F117" s="46" t="e">
+      <c r="F117" s="43" t="e">
         <f t="shared" ref="F117:N117" si="43">F116/H20</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G117" s="46" t="e">
+      <c r="G117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H117" s="46" t="e">
+      <c r="H117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I117" s="47" t="e">
+      <c r="I117" s="44" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J117" s="46" t="e">
+      <c r="J117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K117" s="46" t="e">
+      <c r="K117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L117" s="47" t="e">
+      <c r="L117" s="44" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M117" s="46" t="e">
+      <c r="M117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N117" s="46" t="e">
+      <c r="N117" s="43" t="e">
         <f t="shared" si="43"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O117" s="46" t="e">
+      <c r="O117" s="43" t="e">
         <f>O116/#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="P117" s="46" t="e">
+      <c r="P117" s="43" t="e">
         <f>P116/#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:16" ht="19" customHeight="1">
       <c r="A118" t="s">
         <v>115</v>
       </c>
@@ -7333,7 +8183,7 @@
       <c r="O118" s="5"/>
       <c r="P118" s="5"/>
     </row>
-    <row r="119" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:16" ht="19" customHeight="1">
       <c r="A119" t="s">
         <v>116</v>
       </c>
@@ -7353,7 +8203,7 @@
       <c r="O119" s="5"/>
       <c r="P119" s="5"/>
     </row>
-    <row r="120" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:16" ht="19" customHeight="1">
       <c r="A120" t="s">
         <v>117</v>
       </c>
@@ -7376,7 +8226,7 @@
       <c r="O120" s="5"/>
       <c r="P120" s="5"/>
     </row>
-    <row r="121" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:16" ht="19" customHeight="1">
       <c r="A121" t="s">
         <v>118</v>
       </c>
@@ -7396,7 +8246,7 @@
       <c r="O121" s="5"/>
       <c r="P121" s="5"/>
     </row>
-    <row r="122" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:16" ht="19" customHeight="1">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -7416,7 +8266,7 @@
       <c r="O122" s="5"/>
       <c r="P122" s="5"/>
     </row>
-    <row r="123" spans="1:16" ht="19" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:16" ht="19" customHeight="1">
       <c r="A123" t="s">
         <v>120</v>
       </c>
@@ -7440,7 +8290,7 @@
       <c r="O123" s="5"/>
       <c r="P123" s="5"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>122</v>
       </c>
@@ -7460,7 +8310,7 @@
       <c r="O124" s="5"/>
       <c r="P124" s="5"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>123</v>
       </c>
@@ -7480,7 +8330,7 @@
       <c r="O125" s="5"/>
       <c r="P125" s="5"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:16">
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
@@ -7497,7 +8347,7 @@
       <c r="O126" s="5"/>
       <c r="P126" s="5"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>124</v>
       </c>
@@ -7517,7 +8367,7 @@
       <c r="O127" s="5"/>
       <c r="P127" s="5"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>125</v>
       </c>
@@ -7539,7 +8389,7 @@
       <c r="O128" s="5"/>
       <c r="P128" s="5"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
         <v>126</v>
       </c>
@@ -7561,7 +8411,7 @@
       <c r="O129" s="5"/>
       <c r="P129" s="5"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>127</v>
       </c>
@@ -7587,7 +8437,7 @@
       <c r="O130" s="5"/>
       <c r="P130" s="5"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
         <v>128</v>
       </c>
@@ -7607,7 +8457,7 @@
       <c r="O131" s="5"/>
       <c r="P131" s="5"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
         <v>129</v>
       </c>
@@ -7629,7 +8479,7 @@
       <c r="O132" s="5"/>
       <c r="P132" s="5"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:16">
       <c r="A133" t="s">
         <v>130</v>
       </c>
@@ -7651,7 +8501,7 @@
       <c r="O133" s="5"/>
       <c r="P133" s="5"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:16">
       <c r="A134" t="s">
         <v>131</v>
       </c>
@@ -7673,7 +8523,7 @@
       <c r="O134" s="5"/>
       <c r="P134" s="5"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:16">
       <c r="A135" t="s">
         <v>132</v>
       </c>
@@ -7693,7 +8543,7 @@
       <c r="O135" s="5"/>
       <c r="P135" s="5"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:16">
       <c r="A136" t="s">
         <v>133</v>
       </c>
@@ -7715,7 +8565,7 @@
       <c r="O136" s="5"/>
       <c r="P136" s="5"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:16">
       <c r="A137" t="s">
         <v>134</v>
       </c>
@@ -7735,7 +8585,7 @@
       <c r="O137" s="5"/>
       <c r="P137" s="5"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>135</v>
       </c>
@@ -7757,7 +8607,7 @@
       <c r="O138" s="5"/>
       <c r="P138" s="5"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:16">
       <c r="A139" t="s">
         <v>136</v>
       </c>
@@ -7777,7 +8627,7 @@
       <c r="O139" s="5"/>
       <c r="P139" s="5"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>137</v>
       </c>
@@ -7795,7 +8645,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F50AB0-CC75-4B91-A5E5-8130E279E918}">
   <dimension ref="A3:N23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28.08203125" customWidth="1"/>
     <col min="4" max="4" width="31.25" customWidth="1"/>
@@ -7803,12 +8653,12 @@
     <col min="10" max="10" width="13.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -7816,7 +8666,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -7824,7 +8674,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>140</v>
       </c>
@@ -7832,7 +8682,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -7840,7 +8690,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>141</v>
       </c>
@@ -7848,7 +8698,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>126</v>
       </c>
@@ -7856,7 +8706,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -7865,7 +8715,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>142</v>
       </c>
@@ -7876,23 +8726,23 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="50">
+      <c r="B13" s="47">
         <v>0.37</v>
       </c>
       <c r="D13" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="47">
         <v>0.3</v>
       </c>
       <c r="G13" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="47">
         <f>H15/H14</f>
         <v>0.28000000000000003</v>
       </c>
@@ -7910,7 +8760,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -7936,7 +8786,7 @@
         <f>H14*0.42</f>
         <v>630</v>
       </c>
-      <c r="L14" s="51" t="s">
+      <c r="L14" s="48" t="s">
         <v>145</v>
       </c>
       <c r="M14" t="s">
@@ -7947,7 +8797,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>153</v>
       </c>
@@ -7970,7 +8820,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="17" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="4:8">
       <c r="D17" t="s">
         <v>154</v>
       </c>
@@ -7978,7 +8828,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="4:8">
       <c r="D18" t="s">
         <v>156</v>
       </c>
@@ -7993,7 +8843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="4:8">
       <c r="D19" t="s">
         <v>157</v>
       </c>
@@ -8008,7 +8858,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="4:8">
       <c r="D20" t="s">
         <v>159</v>
       </c>
@@ -8017,12 +8867,12 @@
         <v>685</v>
       </c>
     </row>
-    <row r="22" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="4:8">
       <c r="D22" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="4:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="4:8">
       <c r="D23">
         <f>E19*10</f>
         <v>5380</v>
@@ -8036,26 +8886,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD6D406-4501-40D9-9742-2F8F9B1D83B9}">
-  <dimension ref="A2:E19"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:F19"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="5" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.5" customWidth="1"/>
+    <col min="7" max="7" width="26.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>148</v>
       </c>
@@ -8065,8 +8917,11 @@
       <c r="E6" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>169</v>
       </c>
@@ -8076,56 +8931,77 @@
       <c r="D7" s="5">
         <v>5500000</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="C8" t="s">
         <v>171</v>
       </c>
       <c r="D8" s="5">
         <v>2000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="C9" t="s">
         <v>172</v>
       </c>
       <c r="D9" s="5">
         <v>1800000</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="C10" t="s">
         <v>175</v>
       </c>
       <c r="D10" s="5">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="C11" t="s">
         <v>173</v>
       </c>
       <c r="D11" s="5">
         <v>500000</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F11" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="C12" t="s">
         <v>174</v>
       </c>
       <c r="D12" s="5">
         <v>300000</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="C13" t="s">
         <v>176</v>
       </c>
       <c r="D13" s="5">
         <v>900000</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -8139,7 +9015,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6">
       <c r="B15" t="s">
         <v>166</v>
       </c>
@@ -8153,8 +9029,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="52" t="s">
+    <row r="16" spans="1:6" ht="54">
+      <c r="B16" s="49" t="s">
         <v>167</v>
       </c>
       <c r="C16" t="s">
@@ -8164,7 +9040,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4">
       <c r="C17" t="s">
         <v>71</v>
       </c>
@@ -8172,7 +9048,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>177</v>
       </c>
@@ -8181,11 +9057,11 @@
         <v>4600000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="53">
+      <c r="D19" s="50">
         <f>D18/D6</f>
         <v>0.38333333333333336</v>
       </c>
@@ -8194,4 +9070,951 @@
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20C973CE-3B00-4632-A7C0-DD1559EE5609}">
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr defaultColWidth="3.33203125" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="3.33203125" style="56"/>
+    <col min="2" max="2" width="29.58203125" style="56" customWidth="1"/>
+    <col min="3" max="3" width="19.25" style="56" customWidth="1"/>
+    <col min="4" max="4" width="23.58203125" style="56" customWidth="1"/>
+    <col min="5" max="7" width="3.33203125" style="56"/>
+    <col min="8" max="8" width="9" style="56" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="56" customWidth="1"/>
+    <col min="10" max="10" width="49" style="56" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" style="56" bestFit="1" customWidth="1"/>
+    <col min="12" max="255" width="3.33203125" style="56"/>
+    <col min="256" max="256" width="29.58203125" style="56" customWidth="1"/>
+    <col min="257" max="257" width="19.25" style="56" customWidth="1"/>
+    <col min="258" max="258" width="23.58203125" style="56" customWidth="1"/>
+    <col min="259" max="511" width="3.33203125" style="56"/>
+    <col min="512" max="512" width="29.58203125" style="56" customWidth="1"/>
+    <col min="513" max="513" width="19.25" style="56" customWidth="1"/>
+    <col min="514" max="514" width="23.58203125" style="56" customWidth="1"/>
+    <col min="515" max="767" width="3.33203125" style="56"/>
+    <col min="768" max="768" width="29.58203125" style="56" customWidth="1"/>
+    <col min="769" max="769" width="19.25" style="56" customWidth="1"/>
+    <col min="770" max="770" width="23.58203125" style="56" customWidth="1"/>
+    <col min="771" max="1023" width="3.33203125" style="56"/>
+    <col min="1024" max="1024" width="29.58203125" style="56" customWidth="1"/>
+    <col min="1025" max="1025" width="19.25" style="56" customWidth="1"/>
+    <col min="1026" max="1026" width="23.58203125" style="56" customWidth="1"/>
+    <col min="1027" max="1279" width="3.33203125" style="56"/>
+    <col min="1280" max="1280" width="29.58203125" style="56" customWidth="1"/>
+    <col min="1281" max="1281" width="19.25" style="56" customWidth="1"/>
+    <col min="1282" max="1282" width="23.58203125" style="56" customWidth="1"/>
+    <col min="1283" max="1535" width="3.33203125" style="56"/>
+    <col min="1536" max="1536" width="29.58203125" style="56" customWidth="1"/>
+    <col min="1537" max="1537" width="19.25" style="56" customWidth="1"/>
+    <col min="1538" max="1538" width="23.58203125" style="56" customWidth="1"/>
+    <col min="1539" max="1791" width="3.33203125" style="56"/>
+    <col min="1792" max="1792" width="29.58203125" style="56" customWidth="1"/>
+    <col min="1793" max="1793" width="19.25" style="56" customWidth="1"/>
+    <col min="1794" max="1794" width="23.58203125" style="56" customWidth="1"/>
+    <col min="1795" max="2047" width="3.33203125" style="56"/>
+    <col min="2048" max="2048" width="29.58203125" style="56" customWidth="1"/>
+    <col min="2049" max="2049" width="19.25" style="56" customWidth="1"/>
+    <col min="2050" max="2050" width="23.58203125" style="56" customWidth="1"/>
+    <col min="2051" max="2303" width="3.33203125" style="56"/>
+    <col min="2304" max="2304" width="29.58203125" style="56" customWidth="1"/>
+    <col min="2305" max="2305" width="19.25" style="56" customWidth="1"/>
+    <col min="2306" max="2306" width="23.58203125" style="56" customWidth="1"/>
+    <col min="2307" max="2559" width="3.33203125" style="56"/>
+    <col min="2560" max="2560" width="29.58203125" style="56" customWidth="1"/>
+    <col min="2561" max="2561" width="19.25" style="56" customWidth="1"/>
+    <col min="2562" max="2562" width="23.58203125" style="56" customWidth="1"/>
+    <col min="2563" max="2815" width="3.33203125" style="56"/>
+    <col min="2816" max="2816" width="29.58203125" style="56" customWidth="1"/>
+    <col min="2817" max="2817" width="19.25" style="56" customWidth="1"/>
+    <col min="2818" max="2818" width="23.58203125" style="56" customWidth="1"/>
+    <col min="2819" max="3071" width="3.33203125" style="56"/>
+    <col min="3072" max="3072" width="29.58203125" style="56" customWidth="1"/>
+    <col min="3073" max="3073" width="19.25" style="56" customWidth="1"/>
+    <col min="3074" max="3074" width="23.58203125" style="56" customWidth="1"/>
+    <col min="3075" max="3327" width="3.33203125" style="56"/>
+    <col min="3328" max="3328" width="29.58203125" style="56" customWidth="1"/>
+    <col min="3329" max="3329" width="19.25" style="56" customWidth="1"/>
+    <col min="3330" max="3330" width="23.58203125" style="56" customWidth="1"/>
+    <col min="3331" max="3583" width="3.33203125" style="56"/>
+    <col min="3584" max="3584" width="29.58203125" style="56" customWidth="1"/>
+    <col min="3585" max="3585" width="19.25" style="56" customWidth="1"/>
+    <col min="3586" max="3586" width="23.58203125" style="56" customWidth="1"/>
+    <col min="3587" max="3839" width="3.33203125" style="56"/>
+    <col min="3840" max="3840" width="29.58203125" style="56" customWidth="1"/>
+    <col min="3841" max="3841" width="19.25" style="56" customWidth="1"/>
+    <col min="3842" max="3842" width="23.58203125" style="56" customWidth="1"/>
+    <col min="3843" max="4095" width="3.33203125" style="56"/>
+    <col min="4096" max="4096" width="29.58203125" style="56" customWidth="1"/>
+    <col min="4097" max="4097" width="19.25" style="56" customWidth="1"/>
+    <col min="4098" max="4098" width="23.58203125" style="56" customWidth="1"/>
+    <col min="4099" max="4351" width="3.33203125" style="56"/>
+    <col min="4352" max="4352" width="29.58203125" style="56" customWidth="1"/>
+    <col min="4353" max="4353" width="19.25" style="56" customWidth="1"/>
+    <col min="4354" max="4354" width="23.58203125" style="56" customWidth="1"/>
+    <col min="4355" max="4607" width="3.33203125" style="56"/>
+    <col min="4608" max="4608" width="29.58203125" style="56" customWidth="1"/>
+    <col min="4609" max="4609" width="19.25" style="56" customWidth="1"/>
+    <col min="4610" max="4610" width="23.58203125" style="56" customWidth="1"/>
+    <col min="4611" max="4863" width="3.33203125" style="56"/>
+    <col min="4864" max="4864" width="29.58203125" style="56" customWidth="1"/>
+    <col min="4865" max="4865" width="19.25" style="56" customWidth="1"/>
+    <col min="4866" max="4866" width="23.58203125" style="56" customWidth="1"/>
+    <col min="4867" max="5119" width="3.33203125" style="56"/>
+    <col min="5120" max="5120" width="29.58203125" style="56" customWidth="1"/>
+    <col min="5121" max="5121" width="19.25" style="56" customWidth="1"/>
+    <col min="5122" max="5122" width="23.58203125" style="56" customWidth="1"/>
+    <col min="5123" max="5375" width="3.33203125" style="56"/>
+    <col min="5376" max="5376" width="29.58203125" style="56" customWidth="1"/>
+    <col min="5377" max="5377" width="19.25" style="56" customWidth="1"/>
+    <col min="5378" max="5378" width="23.58203125" style="56" customWidth="1"/>
+    <col min="5379" max="5631" width="3.33203125" style="56"/>
+    <col min="5632" max="5632" width="29.58203125" style="56" customWidth="1"/>
+    <col min="5633" max="5633" width="19.25" style="56" customWidth="1"/>
+    <col min="5634" max="5634" width="23.58203125" style="56" customWidth="1"/>
+    <col min="5635" max="5887" width="3.33203125" style="56"/>
+    <col min="5888" max="5888" width="29.58203125" style="56" customWidth="1"/>
+    <col min="5889" max="5889" width="19.25" style="56" customWidth="1"/>
+    <col min="5890" max="5890" width="23.58203125" style="56" customWidth="1"/>
+    <col min="5891" max="6143" width="3.33203125" style="56"/>
+    <col min="6144" max="6144" width="29.58203125" style="56" customWidth="1"/>
+    <col min="6145" max="6145" width="19.25" style="56" customWidth="1"/>
+    <col min="6146" max="6146" width="23.58203125" style="56" customWidth="1"/>
+    <col min="6147" max="6399" width="3.33203125" style="56"/>
+    <col min="6400" max="6400" width="29.58203125" style="56" customWidth="1"/>
+    <col min="6401" max="6401" width="19.25" style="56" customWidth="1"/>
+    <col min="6402" max="6402" width="23.58203125" style="56" customWidth="1"/>
+    <col min="6403" max="6655" width="3.33203125" style="56"/>
+    <col min="6656" max="6656" width="29.58203125" style="56" customWidth="1"/>
+    <col min="6657" max="6657" width="19.25" style="56" customWidth="1"/>
+    <col min="6658" max="6658" width="23.58203125" style="56" customWidth="1"/>
+    <col min="6659" max="6911" width="3.33203125" style="56"/>
+    <col min="6912" max="6912" width="29.58203125" style="56" customWidth="1"/>
+    <col min="6913" max="6913" width="19.25" style="56" customWidth="1"/>
+    <col min="6914" max="6914" width="23.58203125" style="56" customWidth="1"/>
+    <col min="6915" max="7167" width="3.33203125" style="56"/>
+    <col min="7168" max="7168" width="29.58203125" style="56" customWidth="1"/>
+    <col min="7169" max="7169" width="19.25" style="56" customWidth="1"/>
+    <col min="7170" max="7170" width="23.58203125" style="56" customWidth="1"/>
+    <col min="7171" max="7423" width="3.33203125" style="56"/>
+    <col min="7424" max="7424" width="29.58203125" style="56" customWidth="1"/>
+    <col min="7425" max="7425" width="19.25" style="56" customWidth="1"/>
+    <col min="7426" max="7426" width="23.58203125" style="56" customWidth="1"/>
+    <col min="7427" max="7679" width="3.33203125" style="56"/>
+    <col min="7680" max="7680" width="29.58203125" style="56" customWidth="1"/>
+    <col min="7681" max="7681" width="19.25" style="56" customWidth="1"/>
+    <col min="7682" max="7682" width="23.58203125" style="56" customWidth="1"/>
+    <col min="7683" max="7935" width="3.33203125" style="56"/>
+    <col min="7936" max="7936" width="29.58203125" style="56" customWidth="1"/>
+    <col min="7937" max="7937" width="19.25" style="56" customWidth="1"/>
+    <col min="7938" max="7938" width="23.58203125" style="56" customWidth="1"/>
+    <col min="7939" max="8191" width="3.33203125" style="56"/>
+    <col min="8192" max="8192" width="29.58203125" style="56" customWidth="1"/>
+    <col min="8193" max="8193" width="19.25" style="56" customWidth="1"/>
+    <col min="8194" max="8194" width="23.58203125" style="56" customWidth="1"/>
+    <col min="8195" max="8447" width="3.33203125" style="56"/>
+    <col min="8448" max="8448" width="29.58203125" style="56" customWidth="1"/>
+    <col min="8449" max="8449" width="19.25" style="56" customWidth="1"/>
+    <col min="8450" max="8450" width="23.58203125" style="56" customWidth="1"/>
+    <col min="8451" max="8703" width="3.33203125" style="56"/>
+    <col min="8704" max="8704" width="29.58203125" style="56" customWidth="1"/>
+    <col min="8705" max="8705" width="19.25" style="56" customWidth="1"/>
+    <col min="8706" max="8706" width="23.58203125" style="56" customWidth="1"/>
+    <col min="8707" max="8959" width="3.33203125" style="56"/>
+    <col min="8960" max="8960" width="29.58203125" style="56" customWidth="1"/>
+    <col min="8961" max="8961" width="19.25" style="56" customWidth="1"/>
+    <col min="8962" max="8962" width="23.58203125" style="56" customWidth="1"/>
+    <col min="8963" max="9215" width="3.33203125" style="56"/>
+    <col min="9216" max="9216" width="29.58203125" style="56" customWidth="1"/>
+    <col min="9217" max="9217" width="19.25" style="56" customWidth="1"/>
+    <col min="9218" max="9218" width="23.58203125" style="56" customWidth="1"/>
+    <col min="9219" max="9471" width="3.33203125" style="56"/>
+    <col min="9472" max="9472" width="29.58203125" style="56" customWidth="1"/>
+    <col min="9473" max="9473" width="19.25" style="56" customWidth="1"/>
+    <col min="9474" max="9474" width="23.58203125" style="56" customWidth="1"/>
+    <col min="9475" max="9727" width="3.33203125" style="56"/>
+    <col min="9728" max="9728" width="29.58203125" style="56" customWidth="1"/>
+    <col min="9729" max="9729" width="19.25" style="56" customWidth="1"/>
+    <col min="9730" max="9730" width="23.58203125" style="56" customWidth="1"/>
+    <col min="9731" max="9983" width="3.33203125" style="56"/>
+    <col min="9984" max="9984" width="29.58203125" style="56" customWidth="1"/>
+    <col min="9985" max="9985" width="19.25" style="56" customWidth="1"/>
+    <col min="9986" max="9986" width="23.58203125" style="56" customWidth="1"/>
+    <col min="9987" max="10239" width="3.33203125" style="56"/>
+    <col min="10240" max="10240" width="29.58203125" style="56" customWidth="1"/>
+    <col min="10241" max="10241" width="19.25" style="56" customWidth="1"/>
+    <col min="10242" max="10242" width="23.58203125" style="56" customWidth="1"/>
+    <col min="10243" max="10495" width="3.33203125" style="56"/>
+    <col min="10496" max="10496" width="29.58203125" style="56" customWidth="1"/>
+    <col min="10497" max="10497" width="19.25" style="56" customWidth="1"/>
+    <col min="10498" max="10498" width="23.58203125" style="56" customWidth="1"/>
+    <col min="10499" max="10751" width="3.33203125" style="56"/>
+    <col min="10752" max="10752" width="29.58203125" style="56" customWidth="1"/>
+    <col min="10753" max="10753" width="19.25" style="56" customWidth="1"/>
+    <col min="10754" max="10754" width="23.58203125" style="56" customWidth="1"/>
+    <col min="10755" max="11007" width="3.33203125" style="56"/>
+    <col min="11008" max="11008" width="29.58203125" style="56" customWidth="1"/>
+    <col min="11009" max="11009" width="19.25" style="56" customWidth="1"/>
+    <col min="11010" max="11010" width="23.58203125" style="56" customWidth="1"/>
+    <col min="11011" max="11263" width="3.33203125" style="56"/>
+    <col min="11264" max="11264" width="29.58203125" style="56" customWidth="1"/>
+    <col min="11265" max="11265" width="19.25" style="56" customWidth="1"/>
+    <col min="11266" max="11266" width="23.58203125" style="56" customWidth="1"/>
+    <col min="11267" max="11519" width="3.33203125" style="56"/>
+    <col min="11520" max="11520" width="29.58203125" style="56" customWidth="1"/>
+    <col min="11521" max="11521" width="19.25" style="56" customWidth="1"/>
+    <col min="11522" max="11522" width="23.58203125" style="56" customWidth="1"/>
+    <col min="11523" max="11775" width="3.33203125" style="56"/>
+    <col min="11776" max="11776" width="29.58203125" style="56" customWidth="1"/>
+    <col min="11777" max="11777" width="19.25" style="56" customWidth="1"/>
+    <col min="11778" max="11778" width="23.58203125" style="56" customWidth="1"/>
+    <col min="11779" max="12031" width="3.33203125" style="56"/>
+    <col min="12032" max="12032" width="29.58203125" style="56" customWidth="1"/>
+    <col min="12033" max="12033" width="19.25" style="56" customWidth="1"/>
+    <col min="12034" max="12034" width="23.58203125" style="56" customWidth="1"/>
+    <col min="12035" max="12287" width="3.33203125" style="56"/>
+    <col min="12288" max="12288" width="29.58203125" style="56" customWidth="1"/>
+    <col min="12289" max="12289" width="19.25" style="56" customWidth="1"/>
+    <col min="12290" max="12290" width="23.58203125" style="56" customWidth="1"/>
+    <col min="12291" max="12543" width="3.33203125" style="56"/>
+    <col min="12544" max="12544" width="29.58203125" style="56" customWidth="1"/>
+    <col min="12545" max="12545" width="19.25" style="56" customWidth="1"/>
+    <col min="12546" max="12546" width="23.58203125" style="56" customWidth="1"/>
+    <col min="12547" max="12799" width="3.33203125" style="56"/>
+    <col min="12800" max="12800" width="29.58203125" style="56" customWidth="1"/>
+    <col min="12801" max="12801" width="19.25" style="56" customWidth="1"/>
+    <col min="12802" max="12802" width="23.58203125" style="56" customWidth="1"/>
+    <col min="12803" max="13055" width="3.33203125" style="56"/>
+    <col min="13056" max="13056" width="29.58203125" style="56" customWidth="1"/>
+    <col min="13057" max="13057" width="19.25" style="56" customWidth="1"/>
+    <col min="13058" max="13058" width="23.58203125" style="56" customWidth="1"/>
+    <col min="13059" max="13311" width="3.33203125" style="56"/>
+    <col min="13312" max="13312" width="29.58203125" style="56" customWidth="1"/>
+    <col min="13313" max="13313" width="19.25" style="56" customWidth="1"/>
+    <col min="13314" max="13314" width="23.58203125" style="56" customWidth="1"/>
+    <col min="13315" max="13567" width="3.33203125" style="56"/>
+    <col min="13568" max="13568" width="29.58203125" style="56" customWidth="1"/>
+    <col min="13569" max="13569" width="19.25" style="56" customWidth="1"/>
+    <col min="13570" max="13570" width="23.58203125" style="56" customWidth="1"/>
+    <col min="13571" max="13823" width="3.33203125" style="56"/>
+    <col min="13824" max="13824" width="29.58203125" style="56" customWidth="1"/>
+    <col min="13825" max="13825" width="19.25" style="56" customWidth="1"/>
+    <col min="13826" max="13826" width="23.58203125" style="56" customWidth="1"/>
+    <col min="13827" max="14079" width="3.33203125" style="56"/>
+    <col min="14080" max="14080" width="29.58203125" style="56" customWidth="1"/>
+    <col min="14081" max="14081" width="19.25" style="56" customWidth="1"/>
+    <col min="14082" max="14082" width="23.58203125" style="56" customWidth="1"/>
+    <col min="14083" max="14335" width="3.33203125" style="56"/>
+    <col min="14336" max="14336" width="29.58203125" style="56" customWidth="1"/>
+    <col min="14337" max="14337" width="19.25" style="56" customWidth="1"/>
+    <col min="14338" max="14338" width="23.58203125" style="56" customWidth="1"/>
+    <col min="14339" max="14591" width="3.33203125" style="56"/>
+    <col min="14592" max="14592" width="29.58203125" style="56" customWidth="1"/>
+    <col min="14593" max="14593" width="19.25" style="56" customWidth="1"/>
+    <col min="14594" max="14594" width="23.58203125" style="56" customWidth="1"/>
+    <col min="14595" max="14847" width="3.33203125" style="56"/>
+    <col min="14848" max="14848" width="29.58203125" style="56" customWidth="1"/>
+    <col min="14849" max="14849" width="19.25" style="56" customWidth="1"/>
+    <col min="14850" max="14850" width="23.58203125" style="56" customWidth="1"/>
+    <col min="14851" max="15103" width="3.33203125" style="56"/>
+    <col min="15104" max="15104" width="29.58203125" style="56" customWidth="1"/>
+    <col min="15105" max="15105" width="19.25" style="56" customWidth="1"/>
+    <col min="15106" max="15106" width="23.58203125" style="56" customWidth="1"/>
+    <col min="15107" max="15359" width="3.33203125" style="56"/>
+    <col min="15360" max="15360" width="29.58203125" style="56" customWidth="1"/>
+    <col min="15361" max="15361" width="19.25" style="56" customWidth="1"/>
+    <col min="15362" max="15362" width="23.58203125" style="56" customWidth="1"/>
+    <col min="15363" max="15615" width="3.33203125" style="56"/>
+    <col min="15616" max="15616" width="29.58203125" style="56" customWidth="1"/>
+    <col min="15617" max="15617" width="19.25" style="56" customWidth="1"/>
+    <col min="15618" max="15618" width="23.58203125" style="56" customWidth="1"/>
+    <col min="15619" max="15871" width="3.33203125" style="56"/>
+    <col min="15872" max="15872" width="29.58203125" style="56" customWidth="1"/>
+    <col min="15873" max="15873" width="19.25" style="56" customWidth="1"/>
+    <col min="15874" max="15874" width="23.58203125" style="56" customWidth="1"/>
+    <col min="15875" max="16127" width="3.33203125" style="56"/>
+    <col min="16128" max="16128" width="29.58203125" style="56" customWidth="1"/>
+    <col min="16129" max="16129" width="19.25" style="56" customWidth="1"/>
+    <col min="16130" max="16130" width="23.58203125" style="56" customWidth="1"/>
+    <col min="16131" max="16384" width="3.33203125" style="56"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="36" customHeight="1">
+      <c r="A1" s="54" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+    </row>
+    <row r="2" spans="1:11" ht="10.5" customHeight="1">
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+    </row>
+    <row r="3" spans="1:11" ht="27" customHeight="1">
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="60"/>
+    </row>
+    <row r="4" spans="1:11" ht="27" customHeight="1">
+      <c r="A4" s="62" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="62"/>
+    </row>
+    <row r="5" spans="1:11" ht="27" customHeight="1">
+      <c r="A5" s="55"/>
+      <c r="B5" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" s="55"/>
+      <c r="H5" s="64"/>
+      <c r="J5" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="K5" s="66">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1">
+      <c r="A6" s="58"/>
+      <c r="B6" s="67" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="68">
+        <v>13847393</v>
+      </c>
+      <c r="D6" s="67"/>
+      <c r="H6" s="64" t="s">
+        <v>185</v>
+      </c>
+      <c r="I6" s="56">
+        <v>22</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="K6" s="66">
+        <v>7624829</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A7" s="58"/>
+      <c r="B7" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="C7" s="70">
+        <v>219192</v>
+      </c>
+      <c r="D7" s="67" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="58"/>
+      <c r="H7" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="56">
+        <v>50</v>
+      </c>
+      <c r="J7" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="K7" s="66">
+        <v>69300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1" thickTop="1">
+      <c r="A8" s="58"/>
+      <c r="B8" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="72">
+        <f>SUM(C6:C7)</f>
+        <v>14066585</v>
+      </c>
+      <c r="D8" s="73"/>
+      <c r="E8" s="58"/>
+      <c r="H8" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="I8" s="56">
+        <v>31</v>
+      </c>
+      <c r="J8" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="K8" s="66">
+        <v>172784</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" customHeight="1">
+      <c r="A9" s="58"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="58"/>
+      <c r="H9" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="I9" s="56">
+        <v>34.5</v>
+      </c>
+      <c r="J9" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="K9" s="66">
+        <v>321891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1">
+      <c r="A10" s="58"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="58"/>
+      <c r="H10" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="I10" s="56">
+        <v>33</v>
+      </c>
+      <c r="J10" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="K10" s="66">
+        <v>131490</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="27" customHeight="1">
+      <c r="A11" s="62" t="s">
+        <v>198</v>
+      </c>
+      <c r="B11" s="62"/>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="58"/>
+      <c r="H11" s="64" t="s">
+        <v>199</v>
+      </c>
+      <c r="I11" s="56">
+        <v>26</v>
+      </c>
+      <c r="J11" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="K11" s="66">
+        <v>44895</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="27" customHeight="1">
+      <c r="A12" s="58"/>
+      <c r="B12" s="63" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="58"/>
+      <c r="H12" s="64" t="s">
+        <v>201</v>
+      </c>
+      <c r="I12" s="56">
+        <v>27</v>
+      </c>
+      <c r="J12" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="K12" s="66">
+        <v>16637</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1">
+      <c r="A13" s="58"/>
+      <c r="B13" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="68">
+        <v>3520000</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="58"/>
+      <c r="H13" s="64" t="s">
+        <v>205</v>
+      </c>
+      <c r="I13" s="56">
+        <v>14</v>
+      </c>
+      <c r="J13" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="K13" s="66">
+        <v>1519076</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1">
+      <c r="A14" s="58"/>
+      <c r="B14" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="68">
+        <v>616000</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="58"/>
+      <c r="H14" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="I14" s="56">
+        <f>SUM(I5:I13)*1.2</f>
+        <v>285</v>
+      </c>
+      <c r="J14" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="K14" s="66">
+        <v>23753</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1">
+      <c r="A15" s="58"/>
+      <c r="B15" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="68">
+        <v>94655</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="58"/>
+      <c r="H15" s="64" t="s">
+        <v>212</v>
+      </c>
+      <c r="I15" s="56">
+        <v>30</v>
+      </c>
+      <c r="J15" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="K15" s="66"/>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1">
+      <c r="A16" s="58"/>
+      <c r="B16" s="67" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="68">
+        <v>116080</v>
+      </c>
+      <c r="D16" s="67" t="s">
+        <v>215</v>
+      </c>
+      <c r="E16" s="58"/>
+      <c r="H16" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="I16" s="56">
+        <v>22</v>
+      </c>
+      <c r="J16" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" s="66">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18" customHeight="1">
+      <c r="A17" s="58"/>
+      <c r="B17" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="C17" s="68">
+        <v>96877</v>
+      </c>
+      <c r="D17" s="67"/>
+      <c r="E17" s="58"/>
+      <c r="J17" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="K17" s="66">
+        <v>42679</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1">
+      <c r="A18" s="58"/>
+      <c r="B18" s="67" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" s="68">
+        <v>193848</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>221</v>
+      </c>
+      <c r="E18" s="58"/>
+      <c r="H18" s="64"/>
+      <c r="J18" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="K18" s="66">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1">
+      <c r="B19" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="68">
+        <v>1648612</v>
+      </c>
+      <c r="D19" s="67"/>
+      <c r="H19" s="64" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="56">
+        <f>SUM(I14:I18)</f>
+        <v>337</v>
+      </c>
+      <c r="J19" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="K19" s="66"/>
+    </row>
+    <row r="20" spans="1:11" ht="18" customHeight="1">
+      <c r="B20" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="68">
+        <v>29700</v>
+      </c>
+      <c r="D20" s="67"/>
+      <c r="J20" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="K20" s="66">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18" customHeight="1">
+      <c r="B21" s="67" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="68">
+        <v>83300</v>
+      </c>
+      <c r="D21" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="J21" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="K21" s="66"/>
+    </row>
+    <row r="22" spans="1:11" ht="18" customHeight="1">
+      <c r="B22" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="C22" s="68">
+        <v>55000</v>
+      </c>
+      <c r="D22" s="67" t="s">
+        <v>231</v>
+      </c>
+      <c r="J22" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="K22" s="66">
+        <v>195140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1">
+      <c r="A23" s="75"/>
+      <c r="B23" s="67" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="68">
+        <v>99000</v>
+      </c>
+      <c r="D23" s="67"/>
+      <c r="E23" s="75"/>
+      <c r="J23" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="K23" s="66">
+        <v>77376</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18" customHeight="1">
+      <c r="A24" s="75"/>
+      <c r="B24" s="67" t="s">
+        <v>235</v>
+      </c>
+      <c r="C24" s="68">
+        <v>33000</v>
+      </c>
+      <c r="D24" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="E24" s="75"/>
+      <c r="J24" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="K24" s="66">
+        <v>15125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1">
+      <c r="B25" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" s="68">
+        <v>250031</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="J25" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="K25" s="66">
+        <v>2061665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18" customHeight="1">
+      <c r="B26" s="67" t="s">
+        <v>241</v>
+      </c>
+      <c r="C26" s="68">
+        <v>55000</v>
+      </c>
+      <c r="D26" s="67" t="s">
+        <v>242</v>
+      </c>
+      <c r="J26" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="K26" s="66">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1">
+      <c r="B27" s="76" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="70">
+        <v>8000</v>
+      </c>
+      <c r="D27" s="67" t="s">
+        <v>245</v>
+      </c>
+      <c r="J27" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="K27" s="66">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A28" s="75"/>
+      <c r="B28" s="69" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="70">
+        <v>33840</v>
+      </c>
+      <c r="D28" s="67"/>
+      <c r="E28" s="75"/>
+      <c r="J28" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="K28" s="66">
+        <v>314846</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18" customHeight="1" thickTop="1">
+      <c r="B29" s="71" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="72">
+        <f>SUM(C13:C28)</f>
+        <v>6932943</v>
+      </c>
+      <c r="D29" s="73"/>
+      <c r="J29" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="K29" s="66">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="18" customHeight="1">
+      <c r="B30" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="C30" s="77">
+        <f>C13</f>
+        <v>3520000</v>
+      </c>
+      <c r="J30" s="65" t="s">
+        <v>251</v>
+      </c>
+      <c r="K30" s="66">
+        <v>79403</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18" customHeight="1">
+      <c r="B31" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="78">
+        <f>C29-C30</f>
+        <v>3412943</v>
+      </c>
+      <c r="J31" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="K31" s="66">
+        <v>2463525</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18" customHeight="1">
+      <c r="B32" s="79" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" s="68">
+        <f>C8*1.1</f>
+        <v>15473243.500000002</v>
+      </c>
+      <c r="J32" s="65"/>
+      <c r="K32" s="66"/>
+    </row>
+    <row r="33" spans="2:11" ht="18" customHeight="1" thickBot="1">
+      <c r="B33" s="80" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="81">
+        <f>C29</f>
+        <v>6932943</v>
+      </c>
+      <c r="J33" s="65"/>
+      <c r="K33" s="66"/>
+    </row>
+    <row r="34" spans="2:11" ht="18" customHeight="1" thickTop="1">
+      <c r="B34" s="82" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="83">
+        <f>C32-C33</f>
+        <v>8540300.5000000019</v>
+      </c>
+      <c r="J34" s="65"/>
+      <c r="K34" s="66"/>
+    </row>
+    <row r="35" spans="2:11" ht="18" customHeight="1">
+      <c r="B35" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="84">
+        <f>100%-C36-C37</f>
+        <v>0.55193990193458797</v>
+      </c>
+      <c r="J35" s="65"/>
+      <c r="K35" s="66"/>
+    </row>
+    <row r="36" spans="2:11" ht="18" customHeight="1">
+      <c r="B36" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="84">
+        <f>C30/C32</f>
+        <v>0.22748947239148662</v>
+      </c>
+      <c r="J36" s="65"/>
+      <c r="K36" s="66"/>
+    </row>
+    <row r="37" spans="2:11" ht="18" customHeight="1">
+      <c r="B37" s="60" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="84">
+        <f>C31/C32</f>
+        <v>0.22057062567392541</v>
+      </c>
+      <c r="J37" s="65"/>
+      <c r="K37" s="66"/>
+    </row>
+    <row r="38" spans="2:11" ht="18" customHeight="1">
+      <c r="J38" s="65"/>
+      <c r="K38" s="66"/>
+    </row>
+    <row r="39" spans="2:11" ht="18" customHeight="1">
+      <c r="J39" s="65"/>
+      <c r="K39" s="66"/>
+    </row>
+    <row r="40" spans="2:11" ht="18">
+      <c r="B40" s="85"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="66"/>
+    </row>
+    <row r="41" spans="2:11" ht="18">
+      <c r="B41" s="60"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="66"/>
+    </row>
+    <row r="42" spans="2:11" ht="18">
+      <c r="B42" s="86"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="66"/>
+    </row>
+    <row r="43" spans="2:11" ht="18">
+      <c r="B43" s="85"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="66"/>
+    </row>
+    <row r="44" spans="2:11" ht="18">
+      <c r="J44" s="65"/>
+      <c r="K44" s="66"/>
+    </row>
+    <row r="45" spans="2:11" ht="18">
+      <c r="J45" s="65"/>
+      <c r="K45" s="66"/>
+    </row>
+    <row r="46" spans="2:11" ht="18">
+      <c r="J46" s="65"/>
+      <c r="K46" s="66"/>
+    </row>
+    <row r="47" spans="2:11" ht="18">
+      <c r="J47" s="65"/>
+      <c r="K47" s="66"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A11:B11"/>
+  </mergeCells>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>